--- a/vragen/fotokeuze.xlsx
+++ b/vragen/fotokeuze.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Links" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fotokeuze'!$A$1:$M$591</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fotokeuze'!$A$1:$N$591</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -62,7 +62,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -104,6 +104,21 @@
         <fgColor rgb="00D6EAD6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8EFD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -137,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -172,6 +187,18 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -25631,7 +25658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M591"/>
+  <dimension ref="A1:N591"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -25647,6 +25674,7 @@
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -25715,6 +25743,11 @@
           <t>Opmerking</t>
         </is>
       </c>
+      <c r="N1" s="13" t="inlineStr">
+        <is>
+          <t>Nu in het spel</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="107.8" customHeight="1">
       <c r="A2" s="3" t="n">
@@ -25770,6 +25803,11 @@
         </is>
       </c>
       <c r="M2" s="9" t="n"/>
+      <c r="N2" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="107.8" customHeight="1">
       <c r="A3" s="3" t="n">
@@ -25815,6 +25853,11 @@
         </is>
       </c>
       <c r="M3" s="9" t="n"/>
+      <c r="N3" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="n">
@@ -25850,6 +25893,11 @@
         </is>
       </c>
       <c r="M4" s="9" t="n"/>
+      <c r="N4" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="107.8" customHeight="1">
       <c r="A5" s="3" t="n">
@@ -25900,6 +25948,11 @@
         </is>
       </c>
       <c r="M5" s="9" t="n"/>
+      <c r="N5" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="107.8" customHeight="1">
       <c r="A6" s="3" t="n">
@@ -25955,6 +26008,11 @@
         </is>
       </c>
       <c r="M6" s="9" t="n"/>
+      <c r="N6" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="107.8" customHeight="1">
       <c r="A7" s="3" t="n">
@@ -26010,6 +26068,11 @@
         </is>
       </c>
       <c r="M7" s="9" t="n"/>
+      <c r="N7" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="107.8" customHeight="1">
       <c r="A8" s="3" t="n">
@@ -26065,6 +26128,11 @@
         </is>
       </c>
       <c r="M8" s="9" t="n"/>
+      <c r="N8" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="107.8" customHeight="1">
       <c r="A9" s="3" t="n">
@@ -26120,6 +26188,11 @@
         </is>
       </c>
       <c r="M9" s="9" t="n"/>
+      <c r="N9" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="3" t="n">
@@ -26155,6 +26228,11 @@
         </is>
       </c>
       <c r="M10" s="9" t="n"/>
+      <c r="N10" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="107.8" customHeight="1">
       <c r="A11" s="3" t="n">
@@ -26210,6 +26288,11 @@
         </is>
       </c>
       <c r="M11" s="9" t="n"/>
+      <c r="N11" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="107.8" customHeight="1">
       <c r="A12" s="3" t="n">
@@ -26265,6 +26348,11 @@
         </is>
       </c>
       <c r="M12" s="9" t="n"/>
+      <c r="N12" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="3" t="n">
@@ -26300,6 +26388,11 @@
         </is>
       </c>
       <c r="M13" s="9" t="n"/>
+      <c r="N13" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="107.8" customHeight="1">
       <c r="A14" s="3" t="n">
@@ -26355,6 +26448,11 @@
         </is>
       </c>
       <c r="M14" s="9" t="n"/>
+      <c r="N14" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="107.8" customHeight="1">
       <c r="A15" s="3" t="n">
@@ -26410,6 +26508,11 @@
         </is>
       </c>
       <c r="M15" s="9" t="n"/>
+      <c r="N15" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="107.8" customHeight="1">
       <c r="A16" s="3" t="n">
@@ -26465,6 +26568,11 @@
         </is>
       </c>
       <c r="M16" s="9" t="n"/>
+      <c r="N16" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="107.8" customHeight="1">
       <c r="A17" s="3" t="n">
@@ -26520,6 +26628,11 @@
         </is>
       </c>
       <c r="M17" s="9" t="n"/>
+      <c r="N17" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="3" t="n">
@@ -26560,6 +26673,11 @@
         </is>
       </c>
       <c r="M18" s="9" t="n"/>
+      <c r="N18" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="107.8" customHeight="1">
       <c r="A19" s="3" t="n">
@@ -26615,6 +26733,11 @@
         </is>
       </c>
       <c r="M19" s="9" t="n"/>
+      <c r="N19" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="107.8" customHeight="1">
       <c r="A20" s="3" t="n">
@@ -26670,6 +26793,11 @@
         </is>
       </c>
       <c r="M20" s="9" t="n"/>
+      <c r="N20" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="107.8" customHeight="1">
       <c r="A21" s="3" t="n">
@@ -26715,6 +26843,11 @@
         </is>
       </c>
       <c r="M21" s="9" t="n"/>
+      <c r="N21" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="107.8" customHeight="1">
       <c r="A22" s="3" t="n">
@@ -26760,6 +26893,11 @@
         </is>
       </c>
       <c r="M22" s="9" t="n"/>
+      <c r="N22" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="107.8" customHeight="1">
       <c r="A23" s="3" t="n">
@@ -26815,6 +26953,11 @@
         </is>
       </c>
       <c r="M23" s="9" t="n"/>
+      <c r="N23" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="107.8" customHeight="1">
       <c r="A24" s="3" t="n">
@@ -26870,6 +27013,11 @@
         </is>
       </c>
       <c r="M24" s="9" t="n"/>
+      <c r="N24" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="3" t="n">
@@ -26905,6 +27053,11 @@
         </is>
       </c>
       <c r="M25" s="9" t="n"/>
+      <c r="N25" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="3" t="n">
@@ -26945,6 +27098,11 @@
         </is>
       </c>
       <c r="M26" s="9" t="n"/>
+      <c r="N26" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="107.8" customHeight="1">
       <c r="A27" s="3" t="n">
@@ -27000,6 +27158,11 @@
         </is>
       </c>
       <c r="M27" s="9" t="n"/>
+      <c r="N27" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="107.8" customHeight="1">
       <c r="A28" s="3" t="n">
@@ -27045,6 +27208,11 @@
         </is>
       </c>
       <c r="M28" s="9" t="n"/>
+      <c r="N28" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="107.8" customHeight="1">
       <c r="A29" s="3" t="n">
@@ -27100,6 +27268,11 @@
         </is>
       </c>
       <c r="M29" s="9" t="n"/>
+      <c r="N29" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="107.8" customHeight="1">
       <c r="A30" s="3" t="n">
@@ -27155,6 +27328,11 @@
         </is>
       </c>
       <c r="M30" s="9" t="n"/>
+      <c r="N30" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="107.8" customHeight="1">
       <c r="A31" s="3" t="n">
@@ -27200,6 +27378,11 @@
         </is>
       </c>
       <c r="M31" s="9" t="n"/>
+      <c r="N31" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="107.8" customHeight="1">
       <c r="A32" s="3" t="n">
@@ -27255,6 +27438,11 @@
         </is>
       </c>
       <c r="M32" s="9" t="n"/>
+      <c r="N32" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="3" t="n">
@@ -27295,6 +27483,11 @@
         </is>
       </c>
       <c r="M33" s="9" t="n"/>
+      <c r="N33" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="107.8" customHeight="1">
       <c r="A34" s="3" t="n">
@@ -27340,6 +27533,11 @@
         </is>
       </c>
       <c r="M34" s="9" t="n"/>
+      <c r="N34" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="107.8" customHeight="1">
       <c r="A35" s="3" t="n">
@@ -27390,6 +27588,11 @@
         </is>
       </c>
       <c r="M35" s="9" t="n"/>
+      <c r="N35" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="107.8" customHeight="1">
       <c r="A36" s="3" t="n">
@@ -27445,6 +27648,11 @@
         </is>
       </c>
       <c r="M36" s="9" t="n"/>
+      <c r="N36" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="3" t="n">
@@ -27485,6 +27693,11 @@
         </is>
       </c>
       <c r="M37" s="9" t="n"/>
+      <c r="N37" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="107.8" customHeight="1">
       <c r="A38" s="3" t="n">
@@ -27540,6 +27753,11 @@
         </is>
       </c>
       <c r="M38" s="9" t="n"/>
+      <c r="N38" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="3" t="n">
@@ -27575,6 +27793,11 @@
         </is>
       </c>
       <c r="M39" s="9" t="n"/>
+      <c r="N39" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="107.8" customHeight="1">
       <c r="A40" s="3" t="n">
@@ -27620,6 +27843,11 @@
         </is>
       </c>
       <c r="M40" s="9" t="n"/>
+      <c r="N40" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="107.8" customHeight="1">
       <c r="A41" s="3" t="n">
@@ -27675,6 +27903,11 @@
         </is>
       </c>
       <c r="M41" s="9" t="n"/>
+      <c r="N41" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="107.8" customHeight="1">
       <c r="A42" s="3" t="n">
@@ -27720,6 +27953,11 @@
         </is>
       </c>
       <c r="M42" s="9" t="n"/>
+      <c r="N42" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="107.8" customHeight="1">
       <c r="A43" s="3" t="n">
@@ -27775,6 +28013,11 @@
         </is>
       </c>
       <c r="M43" s="9" t="n"/>
+      <c r="N43" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="107.8" customHeight="1">
       <c r="A44" s="3" t="n">
@@ -27820,6 +28063,11 @@
         </is>
       </c>
       <c r="M44" s="9" t="n"/>
+      <c r="N44" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="107.8" customHeight="1">
       <c r="A45" s="3" t="n">
@@ -27865,6 +28113,11 @@
         </is>
       </c>
       <c r="M45" s="9" t="n"/>
+      <c r="N45" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="107.8" customHeight="1">
       <c r="A46" s="3" t="n">
@@ -27915,6 +28168,11 @@
         </is>
       </c>
       <c r="M46" s="9" t="n"/>
+      <c r="N46" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="107.8" customHeight="1">
       <c r="A47" s="3" t="n">
@@ -27955,6 +28213,11 @@
         </is>
       </c>
       <c r="M47" s="9" t="n"/>
+      <c r="N47" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="107.8" customHeight="1">
       <c r="A48" s="3" t="n">
@@ -28000,6 +28263,11 @@
         </is>
       </c>
       <c r="M48" s="9" t="n"/>
+      <c r="N48" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="107.8" customHeight="1">
       <c r="A49" s="3" t="n">
@@ -28055,6 +28323,11 @@
         </is>
       </c>
       <c r="M49" s="9" t="n"/>
+      <c r="N49" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="3" t="n">
@@ -28090,6 +28363,11 @@
         </is>
       </c>
       <c r="M50" s="9" t="n"/>
+      <c r="N50" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="107.8" customHeight="1">
       <c r="A51" s="3" t="n">
@@ -28135,6 +28413,11 @@
         </is>
       </c>
       <c r="M51" s="9" t="n"/>
+      <c r="N51" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="3" t="n">
@@ -28175,6 +28458,11 @@
         </is>
       </c>
       <c r="M52" s="9" t="n"/>
+      <c r="N52" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="107.8" customHeight="1">
       <c r="A53" s="3" t="n">
@@ -28230,6 +28518,11 @@
         </is>
       </c>
       <c r="M53" s="9" t="n"/>
+      <c r="N53" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="107.8" customHeight="1">
       <c r="A54" s="3" t="n">
@@ -28270,6 +28563,11 @@
         </is>
       </c>
       <c r="M54" s="9" t="n"/>
+      <c r="N54" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="107.8" customHeight="1">
       <c r="A55" s="3" t="n">
@@ -28315,6 +28613,11 @@
         </is>
       </c>
       <c r="M55" s="9" t="n"/>
+      <c r="N55" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="3" t="n">
@@ -28355,6 +28658,11 @@
         </is>
       </c>
       <c r="M56" s="9" t="n"/>
+      <c r="N56" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="107.8" customHeight="1">
       <c r="A57" s="3" t="n">
@@ -28400,6 +28708,11 @@
         </is>
       </c>
       <c r="M57" s="9" t="n"/>
+      <c r="N57" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="3" t="n">
@@ -28440,6 +28753,11 @@
         </is>
       </c>
       <c r="M58" s="9" t="n"/>
+      <c r="N58" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="107.8" customHeight="1">
       <c r="A59" s="3" t="n">
@@ -28485,6 +28803,11 @@
         </is>
       </c>
       <c r="M59" s="9" t="n"/>
+      <c r="N59" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="107.8" customHeight="1">
       <c r="A60" s="3" t="n">
@@ -28540,6 +28863,11 @@
         </is>
       </c>
       <c r="M60" s="9" t="n"/>
+      <c r="N60" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="3" t="n">
@@ -28580,6 +28908,11 @@
         </is>
       </c>
       <c r="M61" s="9" t="n"/>
+      <c r="N61" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="107.8" customHeight="1">
       <c r="A62" s="3" t="n">
@@ -28635,6 +28968,11 @@
         </is>
       </c>
       <c r="M62" s="9" t="n"/>
+      <c r="N62" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="3" t="n">
@@ -28670,6 +29008,11 @@
         </is>
       </c>
       <c r="M63" s="9" t="n"/>
+      <c r="N63" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="107.8" customHeight="1">
       <c r="A64" s="3" t="n">
@@ -28715,6 +29058,11 @@
         </is>
       </c>
       <c r="M64" s="9" t="n"/>
+      <c r="N64" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="107.8" customHeight="1">
       <c r="A65" s="3" t="n">
@@ -28770,6 +29118,11 @@
         </is>
       </c>
       <c r="M65" s="9" t="n"/>
+      <c r="N65" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="107.8" customHeight="1">
       <c r="A66" s="3" t="n">
@@ -28825,6 +29178,11 @@
         </is>
       </c>
       <c r="M66" s="9" t="n"/>
+      <c r="N66" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="107.8" customHeight="1">
       <c r="A67" s="3" t="n">
@@ -28880,6 +29238,11 @@
         </is>
       </c>
       <c r="M67" s="9" t="n"/>
+      <c r="N67" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="3" t="n">
@@ -28920,6 +29283,11 @@
         </is>
       </c>
       <c r="M68" s="9" t="n"/>
+      <c r="N68" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="3" t="n">
@@ -28955,6 +29323,11 @@
         </is>
       </c>
       <c r="M69" s="9" t="n"/>
+      <c r="N69" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="3" t="n">
@@ -28990,6 +29363,11 @@
         </is>
       </c>
       <c r="M70" s="9" t="n"/>
+      <c r="N70" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="3" t="n">
@@ -29025,6 +29403,11 @@
         </is>
       </c>
       <c r="M71" s="9" t="n"/>
+      <c r="N71" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="3" t="n">
@@ -29060,6 +29443,11 @@
         </is>
       </c>
       <c r="M72" s="9" t="n"/>
+      <c r="N72" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="3" t="n">
@@ -29095,6 +29483,11 @@
         </is>
       </c>
       <c r="M73" s="9" t="n"/>
+      <c r="N73" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="107.8" customHeight="1">
       <c r="A74" s="3" t="n">
@@ -29145,6 +29538,11 @@
         </is>
       </c>
       <c r="M74" s="9" t="n"/>
+      <c r="N74" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="107.8" customHeight="1">
       <c r="A75" s="3" t="n">
@@ -29190,6 +29588,11 @@
         </is>
       </c>
       <c r="M75" s="9" t="n"/>
+      <c r="N75" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="3" t="n">
@@ -29230,6 +29633,11 @@
         </is>
       </c>
       <c r="M76" s="9" t="n"/>
+      <c r="N76" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="107.8" customHeight="1">
       <c r="A77" s="3" t="n">
@@ -29285,6 +29693,11 @@
         </is>
       </c>
       <c r="M77" s="9" t="n"/>
+      <c r="N77" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="107.8" customHeight="1">
       <c r="A78" s="3" t="n">
@@ -29330,6 +29743,11 @@
         </is>
       </c>
       <c r="M78" s="9" t="n"/>
+      <c r="N78" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="3" t="n">
@@ -29365,6 +29783,11 @@
         </is>
       </c>
       <c r="M79" s="9" t="n"/>
+      <c r="N79" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="107.8" customHeight="1">
       <c r="A80" s="3" t="n">
@@ -29410,6 +29833,11 @@
         </is>
       </c>
       <c r="M80" s="9" t="n"/>
+      <c r="N80" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="107.8" customHeight="1">
       <c r="A81" s="3" t="n">
@@ -29465,6 +29893,11 @@
         </is>
       </c>
       <c r="M81" s="9" t="n"/>
+      <c r="N81" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="107.8" customHeight="1">
       <c r="A82" s="3" t="n">
@@ -29510,6 +29943,11 @@
         </is>
       </c>
       <c r="M82" s="9" t="n"/>
+      <c r="N82" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="107.8" customHeight="1">
       <c r="A83" s="3" t="n">
@@ -29565,6 +30003,11 @@
         </is>
       </c>
       <c r="M83" s="9" t="n"/>
+      <c r="N83" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="3" t="n">
@@ -29605,6 +30048,11 @@
         </is>
       </c>
       <c r="M84" s="9" t="n"/>
+      <c r="N84" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="107.8" customHeight="1">
       <c r="A85" s="3" t="n">
@@ -29660,6 +30108,11 @@
         </is>
       </c>
       <c r="M85" s="9" t="n"/>
+      <c r="N85" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="107.8" customHeight="1">
       <c r="A86" s="3" t="n">
@@ -29715,6 +30168,11 @@
         </is>
       </c>
       <c r="M86" s="9" t="n"/>
+      <c r="N86" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="3" t="n">
@@ -29755,6 +30213,11 @@
         </is>
       </c>
       <c r="M87" s="9" t="n"/>
+      <c r="N87" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="107.8" customHeight="1">
       <c r="A88" s="3" t="n">
@@ -29810,6 +30273,11 @@
         </is>
       </c>
       <c r="M88" s="9" t="n"/>
+      <c r="N88" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="107.8" customHeight="1">
       <c r="A89" s="3" t="n">
@@ -29865,6 +30333,11 @@
         </is>
       </c>
       <c r="M89" s="9" t="n"/>
+      <c r="N89" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="107.8" customHeight="1">
       <c r="A90" s="3" t="n">
@@ -29910,6 +30383,11 @@
         </is>
       </c>
       <c r="M90" s="9" t="n"/>
+      <c r="N90" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="107.8" customHeight="1">
       <c r="A91" s="3" t="n">
@@ -29965,6 +30443,11 @@
         </is>
       </c>
       <c r="M91" s="9" t="n"/>
+      <c r="N91" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="3" t="n">
@@ -30005,6 +30488,11 @@
         </is>
       </c>
       <c r="M92" s="9" t="n"/>
+      <c r="N92" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="107.8" customHeight="1">
       <c r="A93" s="3" t="n">
@@ -30050,6 +30538,11 @@
         </is>
       </c>
       <c r="M93" s="9" t="n"/>
+      <c r="N93" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="107.8" customHeight="1">
       <c r="A94" s="3" t="n">
@@ -30105,6 +30598,11 @@
         </is>
       </c>
       <c r="M94" s="9" t="n"/>
+      <c r="N94" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="107.8" customHeight="1">
       <c r="A95" s="3" t="n">
@@ -30145,6 +30643,11 @@
         </is>
       </c>
       <c r="M95" s="9" t="n"/>
+      <c r="N95" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="107.8" customHeight="1">
       <c r="A96" s="3" t="n">
@@ -30190,6 +30693,11 @@
         </is>
       </c>
       <c r="M96" s="9" t="n"/>
+      <c r="N96" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="3" t="n">
@@ -30230,6 +30738,11 @@
         </is>
       </c>
       <c r="M97" s="9" t="n"/>
+      <c r="N97" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="107.8" customHeight="1">
       <c r="A98" s="3" t="n">
@@ -30285,6 +30798,11 @@
         </is>
       </c>
       <c r="M98" s="9" t="n"/>
+      <c r="N98" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="107.8" customHeight="1">
       <c r="A99" s="3" t="n">
@@ -30340,6 +30858,11 @@
         </is>
       </c>
       <c r="M99" s="9" t="n"/>
+      <c r="N99" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="3" t="n">
@@ -30380,6 +30903,11 @@
         </is>
       </c>
       <c r="M100" s="9" t="n"/>
+      <c r="N100" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="107.8" customHeight="1">
       <c r="A101" s="3" t="n">
@@ -30435,6 +30963,11 @@
         </is>
       </c>
       <c r="M101" s="9" t="n"/>
+      <c r="N101" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="3" t="n">
@@ -30475,6 +31008,11 @@
         </is>
       </c>
       <c r="M102" s="9" t="n"/>
+      <c r="N102" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="107.8" customHeight="1">
       <c r="A103" s="3" t="n">
@@ -30530,6 +31068,11 @@
         </is>
       </c>
       <c r="M103" s="9" t="n"/>
+      <c r="N103" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="107.8" customHeight="1">
       <c r="A104" s="3" t="n">
@@ -30575,6 +31118,11 @@
         </is>
       </c>
       <c r="M104" s="9" t="n"/>
+      <c r="N104" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="3" t="n">
@@ -30615,6 +31163,11 @@
         </is>
       </c>
       <c r="M105" s="9" t="n"/>
+      <c r="N105" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="3" t="n">
@@ -30650,6 +31203,11 @@
         </is>
       </c>
       <c r="M106" s="9" t="n"/>
+      <c r="N106" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="107.8" customHeight="1">
       <c r="A107" s="3" t="n">
@@ -30705,6 +31263,11 @@
         </is>
       </c>
       <c r="M107" s="9" t="n"/>
+      <c r="N107" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="107.8" customHeight="1">
       <c r="A108" s="3" t="n">
@@ -30760,6 +31323,11 @@
         </is>
       </c>
       <c r="M108" s="9" t="n"/>
+      <c r="N108" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="30" customHeight="1">
       <c r="A109" s="3" t="n">
@@ -30800,6 +31368,11 @@
         </is>
       </c>
       <c r="M109" s="9" t="n"/>
+      <c r="N109" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="3" t="n">
@@ -30840,6 +31413,11 @@
         </is>
       </c>
       <c r="M110" s="9" t="n"/>
+      <c r="N110" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="107.8" customHeight="1">
       <c r="A111" s="3" t="n">
@@ -30895,6 +31473,11 @@
         </is>
       </c>
       <c r="M111" s="9" t="n"/>
+      <c r="N111" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="107.8" customHeight="1">
       <c r="A112" s="3" t="n">
@@ -30950,6 +31533,11 @@
         </is>
       </c>
       <c r="M112" s="9" t="n"/>
+      <c r="N112" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="30" customHeight="1">
       <c r="A113" s="3" t="n">
@@ -30985,6 +31573,11 @@
         </is>
       </c>
       <c r="M113" s="9" t="n"/>
+      <c r="N113" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="30" customHeight="1">
       <c r="A114" s="3" t="n">
@@ -31025,6 +31618,11 @@
         </is>
       </c>
       <c r="M114" s="9" t="n"/>
+      <c r="N114" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="107.8" customHeight="1">
       <c r="A115" s="3" t="n">
@@ -31080,6 +31678,11 @@
         </is>
       </c>
       <c r="M115" s="9" t="n"/>
+      <c r="N115" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="107.8" customHeight="1">
       <c r="A116" s="3" t="n">
@@ -31135,6 +31738,11 @@
         </is>
       </c>
       <c r="M116" s="9" t="n"/>
+      <c r="N116" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="30" customHeight="1">
       <c r="A117" s="3" t="n">
@@ -31170,6 +31778,11 @@
         </is>
       </c>
       <c r="M117" s="9" t="n"/>
+      <c r="N117" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="107.8" customHeight="1">
       <c r="A118" s="3" t="n">
@@ -31215,6 +31828,11 @@
         </is>
       </c>
       <c r="M118" s="9" t="n"/>
+      <c r="N118" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="107.8" customHeight="1">
       <c r="A119" s="3" t="n">
@@ -31270,6 +31888,11 @@
         </is>
       </c>
       <c r="M119" s="9" t="n"/>
+      <c r="N119" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="107.8" customHeight="1">
       <c r="A120" s="3" t="n">
@@ -31325,6 +31948,11 @@
         </is>
       </c>
       <c r="M120" s="9" t="n"/>
+      <c r="N120" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="107.8" customHeight="1">
       <c r="A121" s="3" t="n">
@@ -31375,6 +32003,11 @@
         </is>
       </c>
       <c r="M121" s="9" t="n"/>
+      <c r="N121" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="107.8" customHeight="1">
       <c r="A122" s="3" t="n">
@@ -31430,6 +32063,11 @@
         </is>
       </c>
       <c r="M122" s="9" t="n"/>
+      <c r="N122" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="107.8" customHeight="1">
       <c r="A123" s="3" t="n">
@@ -31475,6 +32113,11 @@
         </is>
       </c>
       <c r="M123" s="9" t="n"/>
+      <c r="N123" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="3" t="n">
@@ -31510,6 +32153,11 @@
         </is>
       </c>
       <c r="M124" s="9" t="n"/>
+      <c r="N124" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="107.8" customHeight="1">
       <c r="A125" s="3" t="n">
@@ -31555,6 +32203,11 @@
         </is>
       </c>
       <c r="M125" s="9" t="n"/>
+      <c r="N125" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="30" customHeight="1">
       <c r="A126" s="3" t="n">
@@ -31590,6 +32243,11 @@
         </is>
       </c>
       <c r="M126" s="9" t="n"/>
+      <c r="N126" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="107.8" customHeight="1">
       <c r="A127" s="3" t="n">
@@ -31640,6 +32298,11 @@
         </is>
       </c>
       <c r="M127" s="9" t="n"/>
+      <c r="N127" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="107.8" customHeight="1">
       <c r="A128" s="3" t="n">
@@ -31685,6 +32348,11 @@
         </is>
       </c>
       <c r="M128" s="9" t="n"/>
+      <c r="N128" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="3" t="n">
@@ -31725,6 +32393,11 @@
         </is>
       </c>
       <c r="M129" s="9" t="n"/>
+      <c r="N129" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="107.8" customHeight="1">
       <c r="A130" s="3" t="n">
@@ -31780,6 +32453,11 @@
         </is>
       </c>
       <c r="M130" s="9" t="n"/>
+      <c r="N130" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="107.8" customHeight="1">
       <c r="A131" s="3" t="n">
@@ -31830,6 +32508,11 @@
         </is>
       </c>
       <c r="M131" s="9" t="n"/>
+      <c r="N131" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="3" t="n">
@@ -31870,6 +32553,11 @@
         </is>
       </c>
       <c r="M132" s="9" t="n"/>
+      <c r="N132" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="107.8" customHeight="1">
       <c r="A133" s="3" t="n">
@@ -31925,6 +32613,11 @@
         </is>
       </c>
       <c r="M133" s="9" t="n"/>
+      <c r="N133" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="107.8" customHeight="1">
       <c r="A134" s="3" t="n">
@@ -31970,6 +32663,11 @@
         </is>
       </c>
       <c r="M134" s="9" t="n"/>
+      <c r="N134" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="107.8" customHeight="1">
       <c r="A135" s="3" t="n">
@@ -32015,6 +32713,11 @@
         </is>
       </c>
       <c r="M135" s="9" t="n"/>
+      <c r="N135" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="107.8" customHeight="1">
       <c r="A136" s="3" t="n">
@@ -32070,6 +32773,11 @@
         </is>
       </c>
       <c r="M136" s="9" t="n"/>
+      <c r="N136" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="107.8" customHeight="1">
       <c r="A137" s="3" t="n">
@@ -32125,6 +32833,11 @@
         </is>
       </c>
       <c r="M137" s="9" t="n"/>
+      <c r="N137" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="3" t="n">
@@ -32165,6 +32878,11 @@
         </is>
       </c>
       <c r="M138" s="9" t="n"/>
+      <c r="N138" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="107.8" customHeight="1">
       <c r="A139" s="3" t="n">
@@ -32220,6 +32938,11 @@
         </is>
       </c>
       <c r="M139" s="9" t="n"/>
+      <c r="N139" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="107.8" customHeight="1">
       <c r="A140" s="3" t="n">
@@ -32275,6 +32998,11 @@
         </is>
       </c>
       <c r="M140" s="9" t="n"/>
+      <c r="N140" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="107.8" customHeight="1">
       <c r="A141" s="3" t="n">
@@ -32320,6 +33048,11 @@
         </is>
       </c>
       <c r="M141" s="9" t="n"/>
+      <c r="N141" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="107.8" customHeight="1">
       <c r="A142" s="3" t="n">
@@ -32370,6 +33103,11 @@
         </is>
       </c>
       <c r="M142" s="9" t="n"/>
+      <c r="N142" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="107.8" customHeight="1">
       <c r="A143" s="3" t="n">
@@ -32425,6 +33163,11 @@
         </is>
       </c>
       <c r="M143" s="9" t="n"/>
+      <c r="N143" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="3" t="n">
@@ -32465,6 +33208,11 @@
         </is>
       </c>
       <c r="M144" s="9" t="n"/>
+      <c r="N144" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="107.8" customHeight="1">
       <c r="A145" s="3" t="n">
@@ -32520,6 +33268,11 @@
         </is>
       </c>
       <c r="M145" s="9" t="n"/>
+      <c r="N145" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="30" customHeight="1">
       <c r="A146" s="3" t="n">
@@ -32560,6 +33313,11 @@
         </is>
       </c>
       <c r="M146" s="9" t="n"/>
+      <c r="N146" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="107.8" customHeight="1">
       <c r="A147" s="3" t="n">
@@ -32605,6 +33363,11 @@
         </is>
       </c>
       <c r="M147" s="9" t="n"/>
+      <c r="N147" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="30" customHeight="1">
       <c r="A148" s="3" t="n">
@@ -32640,6 +33403,11 @@
         </is>
       </c>
       <c r="M148" s="9" t="n"/>
+      <c r="N148" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="30" customHeight="1">
       <c r="A149" s="3" t="n">
@@ -32675,6 +33443,11 @@
         </is>
       </c>
       <c r="M149" s="9" t="n"/>
+      <c r="N149" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="107.8" customHeight="1">
       <c r="A150" s="3" t="n">
@@ -32725,6 +33498,11 @@
         </is>
       </c>
       <c r="M150" s="9" t="n"/>
+      <c r="N150" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="107.8" customHeight="1">
       <c r="A151" s="3" t="n">
@@ -32770,6 +33548,11 @@
         </is>
       </c>
       <c r="M151" s="9" t="n"/>
+      <c r="N151" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="107.8" customHeight="1">
       <c r="A152" s="3" t="n">
@@ -32825,6 +33608,11 @@
         </is>
       </c>
       <c r="M152" s="9" t="n"/>
+      <c r="N152" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="107.8" customHeight="1">
       <c r="A153" s="3" t="n">
@@ -32880,6 +33668,11 @@
         </is>
       </c>
       <c r="M153" s="9" t="n"/>
+      <c r="N153" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="30" customHeight="1">
       <c r="A154" s="3" t="n">
@@ -32920,6 +33713,11 @@
         </is>
       </c>
       <c r="M154" s="9" t="n"/>
+      <c r="N154" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="107.8" customHeight="1">
       <c r="A155" s="3" t="n">
@@ -32975,6 +33773,11 @@
         </is>
       </c>
       <c r="M155" s="9" t="n"/>
+      <c r="N155" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="107.8" customHeight="1">
       <c r="A156" s="3" t="n">
@@ -33020,6 +33823,11 @@
         </is>
       </c>
       <c r="M156" s="9" t="n"/>
+      <c r="N156" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="107.8" customHeight="1">
       <c r="A157" s="3" t="n">
@@ -33065,6 +33873,11 @@
         </is>
       </c>
       <c r="M157" s="9" t="n"/>
+      <c r="N157" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="107.8" customHeight="1">
       <c r="A158" s="3" t="n">
@@ -33120,6 +33933,11 @@
         </is>
       </c>
       <c r="M158" s="9" t="n"/>
+      <c r="N158" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="107.8" customHeight="1">
       <c r="A159" s="3" t="n">
@@ -33175,6 +33993,11 @@
         </is>
       </c>
       <c r="M159" s="9" t="n"/>
+      <c r="N159" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="107.8" customHeight="1">
       <c r="A160" s="3" t="n">
@@ -33220,6 +34043,11 @@
         </is>
       </c>
       <c r="M160" s="9" t="n"/>
+      <c r="N160" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="107.8" customHeight="1">
       <c r="A161" s="3" t="n">
@@ -33275,6 +34103,11 @@
         </is>
       </c>
       <c r="M161" s="9" t="n"/>
+      <c r="N161" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="30" customHeight="1">
       <c r="A162" s="3" t="n">
@@ -33310,6 +34143,11 @@
         </is>
       </c>
       <c r="M162" s="9" t="n"/>
+      <c r="N162" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="107.8" customHeight="1">
       <c r="A163" s="3" t="n">
@@ -33365,6 +34203,11 @@
         </is>
       </c>
       <c r="M163" s="9" t="n"/>
+      <c r="N163" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="107.8" customHeight="1">
       <c r="A164" s="3" t="n">
@@ -33410,6 +34253,11 @@
         </is>
       </c>
       <c r="M164" s="9" t="n"/>
+      <c r="N164" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="107.8" customHeight="1">
       <c r="A165" s="3" t="n">
@@ -33465,6 +34313,11 @@
         </is>
       </c>
       <c r="M165" s="9" t="n"/>
+      <c r="N165" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="107.8" customHeight="1">
       <c r="A166" s="3" t="n">
@@ -33520,6 +34373,11 @@
         </is>
       </c>
       <c r="M166" s="9" t="n"/>
+      <c r="N166" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="107.8" customHeight="1">
       <c r="A167" s="3" t="n">
@@ -33565,6 +34423,11 @@
         </is>
       </c>
       <c r="M167" s="9" t="n"/>
+      <c r="N167" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="107.8" customHeight="1">
       <c r="A168" s="3" t="n">
@@ -33620,6 +34483,11 @@
         </is>
       </c>
       <c r="M168" s="9" t="n"/>
+      <c r="N168" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="107.8" customHeight="1">
       <c r="A169" s="3" t="n">
@@ -33670,6 +34538,11 @@
         </is>
       </c>
       <c r="M169" s="9" t="n"/>
+      <c r="N169" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="30" customHeight="1">
       <c r="A170" s="3" t="n">
@@ -33710,6 +34583,11 @@
         </is>
       </c>
       <c r="M170" s="9" t="n"/>
+      <c r="N170" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="107.8" customHeight="1">
       <c r="A171" s="3" t="n">
@@ -33760,6 +34638,11 @@
         </is>
       </c>
       <c r="M171" s="9" t="n"/>
+      <c r="N171" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="30" customHeight="1">
       <c r="A172" s="3" t="n">
@@ -33795,6 +34678,11 @@
         </is>
       </c>
       <c r="M172" s="9" t="n"/>
+      <c r="N172" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="107.8" customHeight="1">
       <c r="A173" s="3" t="n">
@@ -33850,6 +34738,11 @@
         </is>
       </c>
       <c r="M173" s="9" t="n"/>
+      <c r="N173" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="107.8" customHeight="1">
       <c r="A174" s="3" t="n">
@@ -33900,6 +34793,11 @@
         </is>
       </c>
       <c r="M174" s="9" t="n"/>
+      <c r="N174" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="30" customHeight="1">
       <c r="A175" s="3" t="n">
@@ -33935,6 +34833,11 @@
         </is>
       </c>
       <c r="M175" s="9" t="n"/>
+      <c r="N175" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="30" customHeight="1">
       <c r="A176" s="3" t="n">
@@ -33970,6 +34873,11 @@
         </is>
       </c>
       <c r="M176" s="9" t="n"/>
+      <c r="N176" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="107.8" customHeight="1">
       <c r="A177" s="3" t="n">
@@ -34025,6 +34933,11 @@
         </is>
       </c>
       <c r="M177" s="9" t="n"/>
+      <c r="N177" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="107.8" customHeight="1">
       <c r="A178" s="3" t="n">
@@ -34070,6 +34983,11 @@
         </is>
       </c>
       <c r="M178" s="9" t="n"/>
+      <c r="N178" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="30" customHeight="1">
       <c r="A179" s="3" t="n">
@@ -34110,6 +35028,11 @@
         </is>
       </c>
       <c r="M179" s="9" t="n"/>
+      <c r="N179" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="107.8" customHeight="1">
       <c r="A180" s="3" t="n">
@@ -34165,6 +35088,11 @@
         </is>
       </c>
       <c r="M180" s="9" t="n"/>
+      <c r="N180" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="30" customHeight="1">
       <c r="A181" s="3" t="n">
@@ -34205,6 +35133,11 @@
         </is>
       </c>
       <c r="M181" s="9" t="n"/>
+      <c r="N181" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="30" customHeight="1">
       <c r="A182" s="3" t="n">
@@ -34245,6 +35178,11 @@
         </is>
       </c>
       <c r="M182" s="9" t="n"/>
+      <c r="N182" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="107.8" customHeight="1">
       <c r="A183" s="3" t="n">
@@ -34300,6 +35238,11 @@
         </is>
       </c>
       <c r="M183" s="9" t="n"/>
+      <c r="N183" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="107.8" customHeight="1">
       <c r="A184" s="3" t="n">
@@ -34345,6 +35288,11 @@
         </is>
       </c>
       <c r="M184" s="9" t="n"/>
+      <c r="N184" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="107.8" customHeight="1">
       <c r="A185" s="3" t="n">
@@ -34400,6 +35348,11 @@
         </is>
       </c>
       <c r="M185" s="9" t="n"/>
+      <c r="N185" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="107.8" customHeight="1">
       <c r="A186" s="3" t="n">
@@ -34445,6 +35398,11 @@
         </is>
       </c>
       <c r="M186" s="9" t="n"/>
+      <c r="N186" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="30" customHeight="1">
       <c r="A187" s="3" t="n">
@@ -34480,6 +35438,11 @@
         </is>
       </c>
       <c r="M187" s="9" t="n"/>
+      <c r="N187" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="107.8" customHeight="1">
       <c r="A188" s="3" t="n">
@@ -34535,6 +35498,11 @@
         </is>
       </c>
       <c r="M188" s="9" t="n"/>
+      <c r="N188" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="107.8" customHeight="1">
       <c r="A189" s="3" t="n">
@@ -34590,6 +35558,11 @@
         </is>
       </c>
       <c r="M189" s="9" t="n"/>
+      <c r="N189" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="107.8" customHeight="1">
       <c r="A190" s="3" t="n">
@@ -34645,6 +35618,11 @@
         </is>
       </c>
       <c r="M190" s="9" t="n"/>
+      <c r="N190" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="107.8" customHeight="1">
       <c r="A191" s="3" t="n">
@@ -34700,6 +35678,11 @@
         </is>
       </c>
       <c r="M191" s="9" t="n"/>
+      <c r="N191" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="107.8" customHeight="1">
       <c r="A192" s="3" t="n">
@@ -34745,6 +35728,11 @@
         </is>
       </c>
       <c r="M192" s="9" t="n"/>
+      <c r="N192" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="107.8" customHeight="1">
       <c r="A193" s="3" t="n">
@@ -34800,6 +35788,11 @@
         </is>
       </c>
       <c r="M193" s="9" t="n"/>
+      <c r="N193" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="30" customHeight="1">
       <c r="A194" s="3" t="n">
@@ -34840,6 +35833,11 @@
         </is>
       </c>
       <c r="M194" s="9" t="n"/>
+      <c r="N194" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="30" customHeight="1">
       <c r="A195" s="3" t="n">
@@ -34880,6 +35878,11 @@
         </is>
       </c>
       <c r="M195" s="9" t="n"/>
+      <c r="N195" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="107.8" customHeight="1">
       <c r="A196" s="3" t="n">
@@ -34925,6 +35928,11 @@
         </is>
       </c>
       <c r="M196" s="9" t="n"/>
+      <c r="N196" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="107.8" customHeight="1">
       <c r="A197" s="3" t="n">
@@ -34970,6 +35978,11 @@
         </is>
       </c>
       <c r="M197" s="9" t="n"/>
+      <c r="N197" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="107.8" customHeight="1">
       <c r="A198" s="3" t="n">
@@ -35025,6 +36038,11 @@
         </is>
       </c>
       <c r="M198" s="9" t="n"/>
+      <c r="N198" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="107.8" customHeight="1">
       <c r="A199" s="3" t="n">
@@ -35080,6 +36098,11 @@
         </is>
       </c>
       <c r="M199" s="9" t="n"/>
+      <c r="N199" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="107.8" customHeight="1">
       <c r="A200" s="3" t="n">
@@ -35130,6 +36153,11 @@
         </is>
       </c>
       <c r="M200" s="9" t="n"/>
+      <c r="N200" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="107.8" customHeight="1">
       <c r="A201" s="3" t="n">
@@ -35175,6 +36203,11 @@
         </is>
       </c>
       <c r="M201" s="9" t="n"/>
+      <c r="N201" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="107.8" customHeight="1">
       <c r="A202" s="3" t="n">
@@ -35230,6 +36263,11 @@
         </is>
       </c>
       <c r="M202" s="9" t="n"/>
+      <c r="N202" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="30" customHeight="1">
       <c r="A203" s="3" t="n">
@@ -35270,6 +36308,11 @@
         </is>
       </c>
       <c r="M203" s="9" t="n"/>
+      <c r="N203" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="30" customHeight="1">
       <c r="A204" s="3" t="n">
@@ -35310,6 +36353,11 @@
         </is>
       </c>
       <c r="M204" s="9" t="n"/>
+      <c r="N204" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="107.8" customHeight="1">
       <c r="A205" s="3" t="n">
@@ -35365,6 +36413,11 @@
         </is>
       </c>
       <c r="M205" s="9" t="n"/>
+      <c r="N205" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="107.8" customHeight="1">
       <c r="A206" s="3" t="n">
@@ -35410,6 +36463,11 @@
         </is>
       </c>
       <c r="M206" s="9" t="n"/>
+      <c r="N206" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="107.8" customHeight="1">
       <c r="A207" s="3" t="n">
@@ -35455,6 +36513,11 @@
         </is>
       </c>
       <c r="M207" s="9" t="n"/>
+      <c r="N207" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="107.8" customHeight="1">
       <c r="A208" s="3" t="n">
@@ -35510,6 +36573,11 @@
         </is>
       </c>
       <c r="M208" s="9" t="n"/>
+      <c r="N208" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="107.8" customHeight="1">
       <c r="A209" s="3" t="n">
@@ -35565,6 +36633,11 @@
         </is>
       </c>
       <c r="M209" s="9" t="n"/>
+      <c r="N209" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="107.8" customHeight="1">
       <c r="A210" s="3" t="n">
@@ -35610,6 +36683,11 @@
         </is>
       </c>
       <c r="M210" s="9" t="n"/>
+      <c r="N210" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="107.8" customHeight="1">
       <c r="A211" s="3" t="n">
@@ -35660,6 +36738,11 @@
         </is>
       </c>
       <c r="M211" s="9" t="n"/>
+      <c r="N211" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="107.8" customHeight="1">
       <c r="A212" s="3" t="n">
@@ -35715,6 +36798,11 @@
         </is>
       </c>
       <c r="M212" s="9" t="n"/>
+      <c r="N212" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="107.8" customHeight="1">
       <c r="A213" s="3" t="n">
@@ -35770,6 +36858,11 @@
         </is>
       </c>
       <c r="M213" s="9" t="n"/>
+      <c r="N213" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="107.8" customHeight="1">
       <c r="A214" s="3" t="n">
@@ -35820,6 +36913,11 @@
         </is>
       </c>
       <c r="M214" s="9" t="n"/>
+      <c r="N214" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="107.8" customHeight="1">
       <c r="A215" s="3" t="n">
@@ -35875,6 +36973,11 @@
         </is>
       </c>
       <c r="M215" s="9" t="n"/>
+      <c r="N215" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="107.8" customHeight="1">
       <c r="A216" s="3" t="n">
@@ -35925,6 +37028,11 @@
         </is>
       </c>
       <c r="M216" s="9" t="n"/>
+      <c r="N216" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="107.8" customHeight="1">
       <c r="A217" s="3" t="n">
@@ -35980,6 +37088,11 @@
         </is>
       </c>
       <c r="M217" s="9" t="n"/>
+      <c r="N217" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="107.8" customHeight="1">
       <c r="A218" s="3" t="n">
@@ -36035,6 +37148,11 @@
         </is>
       </c>
       <c r="M218" s="9" t="n"/>
+      <c r="N218" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="30" customHeight="1">
       <c r="A219" s="3" t="n">
@@ -36070,6 +37188,11 @@
         </is>
       </c>
       <c r="M219" s="9" t="n"/>
+      <c r="N219" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="107.8" customHeight="1">
       <c r="A220" s="3" t="n">
@@ -36115,6 +37238,11 @@
         </is>
       </c>
       <c r="M220" s="9" t="n"/>
+      <c r="N220" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="30" customHeight="1">
       <c r="A221" s="3" t="n">
@@ -36150,6 +37278,11 @@
         </is>
       </c>
       <c r="M221" s="9" t="n"/>
+      <c r="N221" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="30" customHeight="1">
       <c r="A222" s="3" t="n">
@@ -36190,6 +37323,11 @@
         </is>
       </c>
       <c r="M222" s="9" t="n"/>
+      <c r="N222" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="107.8" customHeight="1">
       <c r="A223" s="3" t="n">
@@ -36245,6 +37383,11 @@
         </is>
       </c>
       <c r="M223" s="9" t="n"/>
+      <c r="N223" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="107.8" customHeight="1">
       <c r="A224" s="3" t="n">
@@ -36300,6 +37443,11 @@
         </is>
       </c>
       <c r="M224" s="9" t="n"/>
+      <c r="N224" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="225" ht="30" customHeight="1">
       <c r="A225" s="3" t="n">
@@ -36340,6 +37488,11 @@
         </is>
       </c>
       <c r="M225" s="9" t="n"/>
+      <c r="N225" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="107.8" customHeight="1">
       <c r="A226" s="3" t="n">
@@ -36395,6 +37548,11 @@
         </is>
       </c>
       <c r="M226" s="9" t="n"/>
+      <c r="N226" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="107.8" customHeight="1">
       <c r="A227" s="3" t="n">
@@ -36440,6 +37598,11 @@
         </is>
       </c>
       <c r="M227" s="9" t="n"/>
+      <c r="N227" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="107.8" customHeight="1">
       <c r="A228" s="3" t="n">
@@ -36495,6 +37658,11 @@
         </is>
       </c>
       <c r="M228" s="9" t="n"/>
+      <c r="N228" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="107.8" customHeight="1">
       <c r="A229" s="3" t="n">
@@ -36550,6 +37718,11 @@
         </is>
       </c>
       <c r="M229" s="9" t="n"/>
+      <c r="N229" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="30" customHeight="1">
       <c r="A230" s="3" t="n">
@@ -36590,6 +37763,11 @@
         </is>
       </c>
       <c r="M230" s="9" t="n"/>
+      <c r="N230" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="107.8" customHeight="1">
       <c r="A231" s="3" t="n">
@@ -36645,6 +37823,11 @@
         </is>
       </c>
       <c r="M231" s="9" t="n"/>
+      <c r="N231" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="107.8" customHeight="1">
       <c r="A232" s="3" t="n">
@@ -36700,6 +37883,11 @@
         </is>
       </c>
       <c r="M232" s="9" t="n"/>
+      <c r="N232" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="30" customHeight="1">
       <c r="A233" s="3" t="n">
@@ -36740,6 +37928,11 @@
         </is>
       </c>
       <c r="M233" s="9" t="n"/>
+      <c r="N233" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="107.8" customHeight="1">
       <c r="A234" s="3" t="n">
@@ -36795,6 +37988,11 @@
         </is>
       </c>
       <c r="M234" s="9" t="n"/>
+      <c r="N234" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="107.8" customHeight="1">
       <c r="A235" s="3" t="n">
@@ -36850,6 +38048,11 @@
         </is>
       </c>
       <c r="M235" s="9" t="n"/>
+      <c r="N235" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="30" customHeight="1">
       <c r="A236" s="3" t="n">
@@ -36890,6 +38093,11 @@
         </is>
       </c>
       <c r="M236" s="9" t="n"/>
+      <c r="N236" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="107.8" customHeight="1">
       <c r="A237" s="3" t="n">
@@ -36945,6 +38153,11 @@
         </is>
       </c>
       <c r="M237" s="9" t="n"/>
+      <c r="N237" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="107.8" customHeight="1">
       <c r="A238" s="3" t="n">
@@ -36990,6 +38203,11 @@
         </is>
       </c>
       <c r="M238" s="9" t="n"/>
+      <c r="N238" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="107.8" customHeight="1">
       <c r="A239" s="3" t="n">
@@ -37045,6 +38263,11 @@
         </is>
       </c>
       <c r="M239" s="9" t="n"/>
+      <c r="N239" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="240" ht="107.8" customHeight="1">
       <c r="A240" s="3" t="n">
@@ -37090,6 +38313,11 @@
         </is>
       </c>
       <c r="M240" s="9" t="n"/>
+      <c r="N240" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="241" ht="107.8" customHeight="1">
       <c r="A241" s="3" t="n">
@@ -37135,6 +38363,11 @@
         </is>
       </c>
       <c r="M241" s="9" t="n"/>
+      <c r="N241" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="107.8" customHeight="1">
       <c r="A242" s="3" t="n">
@@ -37185,6 +38418,11 @@
         </is>
       </c>
       <c r="M242" s="9" t="n"/>
+      <c r="N242" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="107.8" customHeight="1">
       <c r="A243" s="3" t="n">
@@ -37240,6 +38478,11 @@
         </is>
       </c>
       <c r="M243" s="9" t="n"/>
+      <c r="N243" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="107.8" customHeight="1">
       <c r="A244" s="3" t="n">
@@ -37295,6 +38538,11 @@
         </is>
       </c>
       <c r="M244" s="9" t="n"/>
+      <c r="N244" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="30" customHeight="1">
       <c r="A245" s="3" t="n">
@@ -37335,6 +38583,11 @@
         </is>
       </c>
       <c r="M245" s="9" t="n"/>
+      <c r="N245" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="107.8" customHeight="1">
       <c r="A246" s="3" t="n">
@@ -37390,6 +38643,11 @@
         </is>
       </c>
       <c r="M246" s="9" t="n"/>
+      <c r="N246" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="107.8" customHeight="1">
       <c r="A247" s="3" t="n">
@@ -37435,6 +38693,11 @@
         </is>
       </c>
       <c r="M247" s="9" t="n"/>
+      <c r="N247" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="248" ht="107.8" customHeight="1">
       <c r="A248" s="3" t="n">
@@ -37490,6 +38753,11 @@
         </is>
       </c>
       <c r="M248" s="9" t="n"/>
+      <c r="N248" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="249" ht="107.8" customHeight="1">
       <c r="A249" s="3" t="n">
@@ -37545,6 +38813,11 @@
         </is>
       </c>
       <c r="M249" s="9" t="n"/>
+      <c r="N249" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="30" customHeight="1">
       <c r="A250" s="3" t="n">
@@ -37580,6 +38853,11 @@
         </is>
       </c>
       <c r="M250" s="9" t="n"/>
+      <c r="N250" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="107.8" customHeight="1">
       <c r="A251" s="3" t="n">
@@ -37625,6 +38903,11 @@
         </is>
       </c>
       <c r="M251" s="9" t="n"/>
+      <c r="N251" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="107.8" customHeight="1">
       <c r="A252" s="3" t="n">
@@ -37670,6 +38953,11 @@
         </is>
       </c>
       <c r="M252" s="9" t="n"/>
+      <c r="N252" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="30" customHeight="1">
       <c r="A253" s="3" t="n">
@@ -37710,6 +38998,11 @@
         </is>
       </c>
       <c r="M253" s="9" t="n"/>
+      <c r="N253" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="107.8" customHeight="1">
       <c r="A254" s="3" t="n">
@@ -37755,6 +39048,11 @@
         </is>
       </c>
       <c r="M254" s="9" t="n"/>
+      <c r="N254" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="107.8" customHeight="1">
       <c r="A255" s="3" t="n">
@@ -37805,6 +39103,11 @@
         </is>
       </c>
       <c r="M255" s="9" t="n"/>
+      <c r="N255" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="107.8" customHeight="1">
       <c r="A256" s="3" t="n">
@@ -37855,6 +39158,11 @@
         </is>
       </c>
       <c r="M256" s="9" t="n"/>
+      <c r="N256" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="30" customHeight="1">
       <c r="A257" s="3" t="n">
@@ -37890,6 +39198,11 @@
         </is>
       </c>
       <c r="M257" s="9" t="n"/>
+      <c r="N257" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="30" customHeight="1">
       <c r="A258" s="3" t="n">
@@ -37930,6 +39243,11 @@
         </is>
       </c>
       <c r="M258" s="9" t="n"/>
+      <c r="N258" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="30" customHeight="1">
       <c r="A259" s="3" t="n">
@@ -37970,6 +39288,11 @@
         </is>
       </c>
       <c r="M259" s="9" t="n"/>
+      <c r="N259" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="30" customHeight="1">
       <c r="A260" s="3" t="n">
@@ -38010,6 +39333,11 @@
         </is>
       </c>
       <c r="M260" s="9" t="n"/>
+      <c r="N260" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="261" ht="30" customHeight="1">
       <c r="A261" s="3" t="n">
@@ -38050,6 +39378,11 @@
         </is>
       </c>
       <c r="M261" s="9" t="n"/>
+      <c r="N261" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="107.8" customHeight="1">
       <c r="A262" s="3" t="n">
@@ -38105,6 +39438,11 @@
         </is>
       </c>
       <c r="M262" s="9" t="n"/>
+      <c r="N262" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="263" ht="107.8" customHeight="1">
       <c r="A263" s="3" t="n">
@@ -38160,6 +39498,11 @@
         </is>
       </c>
       <c r="M263" s="9" t="n"/>
+      <c r="N263" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="264" ht="107.8" customHeight="1">
       <c r="A264" s="3" t="n">
@@ -38215,6 +39558,11 @@
         </is>
       </c>
       <c r="M264" s="9" t="n"/>
+      <c r="N264" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="265" ht="30" customHeight="1">
       <c r="A265" s="3" t="n">
@@ -38250,6 +39598,11 @@
         </is>
       </c>
       <c r="M265" s="9" t="n"/>
+      <c r="N265" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="266" ht="30" customHeight="1">
       <c r="A266" s="3" t="n">
@@ -38285,6 +39638,11 @@
         </is>
       </c>
       <c r="M266" s="9" t="n"/>
+      <c r="N266" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="267" ht="107.8" customHeight="1">
       <c r="A267" s="3" t="n">
@@ -38330,6 +39688,11 @@
         </is>
       </c>
       <c r="M267" s="9" t="n"/>
+      <c r="N267" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="268" ht="30" customHeight="1">
       <c r="A268" s="3" t="n">
@@ -38370,6 +39733,11 @@
         </is>
       </c>
       <c r="M268" s="9" t="n"/>
+      <c r="N268" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="269" ht="107.8" customHeight="1">
       <c r="A269" s="3" t="n">
@@ -38415,6 +39783,11 @@
         </is>
       </c>
       <c r="M269" s="9" t="n"/>
+      <c r="N269" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="270" ht="107.8" customHeight="1">
       <c r="A270" s="3" t="n">
@@ -38470,6 +39843,11 @@
         </is>
       </c>
       <c r="M270" s="9" t="n"/>
+      <c r="N270" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="271" ht="107.8" customHeight="1">
       <c r="A271" s="3" t="n">
@@ -38520,6 +39898,11 @@
         </is>
       </c>
       <c r="M271" s="9" t="n"/>
+      <c r="N271" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="272" ht="30" customHeight="1">
       <c r="A272" s="3" t="n">
@@ -38560,6 +39943,11 @@
         </is>
       </c>
       <c r="M272" s="9" t="n"/>
+      <c r="N272" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="30" customHeight="1">
       <c r="A273" s="3" t="n">
@@ -38600,6 +39988,11 @@
         </is>
       </c>
       <c r="M273" s="9" t="n"/>
+      <c r="N273" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="274" ht="107.8" customHeight="1">
       <c r="A274" s="3" t="n">
@@ -38655,6 +40048,11 @@
         </is>
       </c>
       <c r="M274" s="9" t="n"/>
+      <c r="N274" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="275" ht="107.8" customHeight="1">
       <c r="A275" s="3" t="n">
@@ -38700,6 +40098,11 @@
         </is>
       </c>
       <c r="M275" s="9" t="n"/>
+      <c r="N275" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="276" ht="30" customHeight="1">
       <c r="A276" s="3" t="n">
@@ -38740,6 +40143,11 @@
         </is>
       </c>
       <c r="M276" s="9" t="n"/>
+      <c r="N276" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="277" ht="107.8" customHeight="1">
       <c r="A277" s="3" t="n">
@@ -38795,6 +40203,11 @@
         </is>
       </c>
       <c r="M277" s="9" t="n"/>
+      <c r="N277" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="278" ht="107.8" customHeight="1">
       <c r="A278" s="3" t="n">
@@ -38840,6 +40253,11 @@
         </is>
       </c>
       <c r="M278" s="9" t="n"/>
+      <c r="N278" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="279" ht="107.8" customHeight="1">
       <c r="A279" s="3" t="n">
@@ -38895,6 +40313,11 @@
         </is>
       </c>
       <c r="M279" s="9" t="n"/>
+      <c r="N279" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="280" ht="107.8" customHeight="1">
       <c r="A280" s="3" t="n">
@@ -38950,6 +40373,11 @@
         </is>
       </c>
       <c r="M280" s="9" t="n"/>
+      <c r="N280" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="281" ht="30" customHeight="1">
       <c r="A281" s="3" t="n">
@@ -38990,6 +40418,11 @@
         </is>
       </c>
       <c r="M281" s="9" t="n"/>
+      <c r="N281" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="282" ht="30" customHeight="1">
       <c r="A282" s="3" t="n">
@@ -39025,6 +40458,11 @@
         </is>
       </c>
       <c r="M282" s="9" t="n"/>
+      <c r="N282" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="283" ht="107.8" customHeight="1">
       <c r="A283" s="3" t="n">
@@ -39080,6 +40518,11 @@
         </is>
       </c>
       <c r="M283" s="9" t="n"/>
+      <c r="N283" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="284" ht="107.8" customHeight="1">
       <c r="A284" s="3" t="n">
@@ -39135,6 +40578,11 @@
         </is>
       </c>
       <c r="M284" s="9" t="n"/>
+      <c r="N284" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="285" ht="107.8" customHeight="1">
       <c r="A285" s="3" t="n">
@@ -39180,6 +40628,11 @@
         </is>
       </c>
       <c r="M285" s="9" t="n"/>
+      <c r="N285" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="286" ht="107.8" customHeight="1">
       <c r="A286" s="3" t="n">
@@ -39225,6 +40678,11 @@
         </is>
       </c>
       <c r="M286" s="9" t="n"/>
+      <c r="N286" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="287" ht="107.8" customHeight="1">
       <c r="A287" s="3" t="n">
@@ -39280,6 +40738,11 @@
         </is>
       </c>
       <c r="M287" s="9" t="n"/>
+      <c r="N287" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="288" ht="30" customHeight="1">
       <c r="A288" s="3" t="n">
@@ -39320,6 +40783,11 @@
         </is>
       </c>
       <c r="M288" s="9" t="n"/>
+      <c r="N288" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="289" ht="30" customHeight="1">
       <c r="A289" s="3" t="n">
@@ -39360,6 +40828,11 @@
         </is>
       </c>
       <c r="M289" s="9" t="n"/>
+      <c r="N289" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="290" ht="107.8" customHeight="1">
       <c r="A290" s="3" t="n">
@@ -39415,6 +40888,11 @@
         </is>
       </c>
       <c r="M290" s="9" t="n"/>
+      <c r="N290" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="291" ht="30" customHeight="1">
       <c r="A291" s="3" t="n">
@@ -39455,6 +40933,11 @@
         </is>
       </c>
       <c r="M291" s="9" t="n"/>
+      <c r="N291" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="292" ht="30" customHeight="1">
       <c r="A292" s="3" t="n">
@@ -39495,6 +40978,11 @@
         </is>
       </c>
       <c r="M292" s="9" t="n"/>
+      <c r="N292" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="293" ht="107.8" customHeight="1">
       <c r="A293" s="3" t="n">
@@ -39550,6 +41038,11 @@
         </is>
       </c>
       <c r="M293" s="9" t="n"/>
+      <c r="N293" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="294" ht="107.8" customHeight="1">
       <c r="A294" s="3" t="n">
@@ -39605,6 +41098,11 @@
         </is>
       </c>
       <c r="M294" s="9" t="n"/>
+      <c r="N294" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="295" ht="30" customHeight="1">
       <c r="A295" s="3" t="n">
@@ -39645,6 +41143,11 @@
         </is>
       </c>
       <c r="M295" s="9" t="n"/>
+      <c r="N295" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="296" ht="107.8" customHeight="1">
       <c r="A296" s="3" t="n">
@@ -39695,6 +41198,11 @@
         </is>
       </c>
       <c r="M296" s="9" t="n"/>
+      <c r="N296" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="297" ht="30" customHeight="1">
       <c r="A297" s="3" t="n">
@@ -39735,6 +41243,11 @@
         </is>
       </c>
       <c r="M297" s="9" t="n"/>
+      <c r="N297" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="298" ht="107.8" customHeight="1">
       <c r="A298" s="3" t="n">
@@ -39780,6 +41293,11 @@
         </is>
       </c>
       <c r="M298" s="9" t="n"/>
+      <c r="N298" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="299" ht="30" customHeight="1">
       <c r="A299" s="3" t="n">
@@ -39815,6 +41333,11 @@
         </is>
       </c>
       <c r="M299" s="9" t="n"/>
+      <c r="N299" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="300" ht="107.8" customHeight="1">
       <c r="A300" s="3" t="n">
@@ -39870,6 +41393,11 @@
         </is>
       </c>
       <c r="M300" s="9" t="n"/>
+      <c r="N300" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="301" ht="107.8" customHeight="1">
       <c r="A301" s="3" t="n">
@@ -39915,6 +41443,11 @@
         </is>
       </c>
       <c r="M301" s="9" t="n"/>
+      <c r="N301" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="302" ht="107.8" customHeight="1">
       <c r="A302" s="3" t="n">
@@ -39970,6 +41503,11 @@
         </is>
       </c>
       <c r="M302" s="9" t="n"/>
+      <c r="N302" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="303" ht="107.8" customHeight="1">
       <c r="A303" s="3" t="n">
@@ -40025,6 +41563,11 @@
         </is>
       </c>
       <c r="M303" s="9" t="n"/>
+      <c r="N303" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="304" ht="30" customHeight="1">
       <c r="A304" s="3" t="n">
@@ -40060,6 +41603,11 @@
         </is>
       </c>
       <c r="M304" s="9" t="n"/>
+      <c r="N304" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="305" ht="107.8" customHeight="1">
       <c r="A305" s="3" t="n">
@@ -40110,6 +41658,11 @@
         </is>
       </c>
       <c r="M305" s="9" t="n"/>
+      <c r="N305" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="306" ht="107.8" customHeight="1">
       <c r="A306" s="3" t="n">
@@ -40155,6 +41708,11 @@
         </is>
       </c>
       <c r="M306" s="9" t="n"/>
+      <c r="N306" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="307" ht="107.8" customHeight="1">
       <c r="A307" s="3" t="n">
@@ -40200,6 +41758,11 @@
         </is>
       </c>
       <c r="M307" s="9" t="n"/>
+      <c r="N307" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="308" ht="30" customHeight="1">
       <c r="A308" s="3" t="n">
@@ -40235,6 +41798,11 @@
         </is>
       </c>
       <c r="M308" s="9" t="n"/>
+      <c r="N308" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="309" ht="107.8" customHeight="1">
       <c r="A309" s="3" t="n">
@@ -40285,6 +41853,11 @@
         </is>
       </c>
       <c r="M309" s="9" t="n"/>
+      <c r="N309" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="310" ht="107.8" customHeight="1">
       <c r="A310" s="3" t="n">
@@ -40340,6 +41913,11 @@
         </is>
       </c>
       <c r="M310" s="9" t="n"/>
+      <c r="N310" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="311" ht="30" customHeight="1">
       <c r="A311" s="3" t="n">
@@ -40380,6 +41958,11 @@
         </is>
       </c>
       <c r="M311" s="9" t="n"/>
+      <c r="N311" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="312" ht="107.8" customHeight="1">
       <c r="A312" s="3" t="n">
@@ -40435,6 +42018,11 @@
         </is>
       </c>
       <c r="M312" s="9" t="n"/>
+      <c r="N312" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="313" ht="107.8" customHeight="1">
       <c r="A313" s="3" t="n">
@@ -40480,6 +42068,11 @@
         </is>
       </c>
       <c r="M313" s="9" t="n"/>
+      <c r="N313" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="314" ht="107.8" customHeight="1">
       <c r="A314" s="3" t="n">
@@ -40525,6 +42118,11 @@
         </is>
       </c>
       <c r="M314" s="9" t="n"/>
+      <c r="N314" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="315" ht="107.8" customHeight="1">
       <c r="A315" s="3" t="n">
@@ -40580,6 +42178,11 @@
         </is>
       </c>
       <c r="M315" s="9" t="n"/>
+      <c r="N315" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="316" ht="107.8" customHeight="1">
       <c r="A316" s="3" t="n">
@@ -40635,6 +42238,11 @@
         </is>
       </c>
       <c r="M316" s="9" t="n"/>
+      <c r="N316" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="317" ht="30" customHeight="1">
       <c r="A317" s="3" t="n">
@@ -40670,6 +42278,11 @@
         </is>
       </c>
       <c r="M317" s="9" t="n"/>
+      <c r="N317" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="318" ht="30" customHeight="1">
       <c r="A318" s="3" t="n">
@@ -40710,6 +42323,11 @@
         </is>
       </c>
       <c r="M318" s="9" t="n"/>
+      <c r="N318" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="319" ht="107.8" customHeight="1">
       <c r="A319" s="3" t="n">
@@ -40765,6 +42383,11 @@
         </is>
       </c>
       <c r="M319" s="9" t="n"/>
+      <c r="N319" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="320" ht="107.8" customHeight="1">
       <c r="A320" s="3" t="n">
@@ -40820,6 +42443,11 @@
         </is>
       </c>
       <c r="M320" s="9" t="n"/>
+      <c r="N320" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="321" ht="30" customHeight="1">
       <c r="A321" s="3" t="n">
@@ -40860,6 +42488,11 @@
         </is>
       </c>
       <c r="M321" s="9" t="n"/>
+      <c r="N321" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="322" ht="107.8" customHeight="1">
       <c r="A322" s="3" t="n">
@@ -40915,6 +42548,11 @@
         </is>
       </c>
       <c r="M322" s="9" t="n"/>
+      <c r="N322" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="323" ht="30" customHeight="1">
       <c r="A323" s="3" t="n">
@@ -40955,6 +42593,11 @@
         </is>
       </c>
       <c r="M323" s="9" t="n"/>
+      <c r="N323" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="324" ht="107.8" customHeight="1">
       <c r="A324" s="3" t="n">
@@ -41000,6 +42643,11 @@
         </is>
       </c>
       <c r="M324" s="9" t="n"/>
+      <c r="N324" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="325" ht="107.8" customHeight="1">
       <c r="A325" s="3" t="n">
@@ -41055,6 +42703,11 @@
         </is>
       </c>
       <c r="M325" s="9" t="n"/>
+      <c r="N325" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="326" ht="107.8" customHeight="1">
       <c r="A326" s="3" t="n">
@@ -41110,6 +42763,11 @@
         </is>
       </c>
       <c r="M326" s="9" t="n"/>
+      <c r="N326" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="327" ht="107.8" customHeight="1">
       <c r="A327" s="3" t="n">
@@ -41165,6 +42823,11 @@
         </is>
       </c>
       <c r="M327" s="9" t="n"/>
+      <c r="N327" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="328" ht="107.8" customHeight="1">
       <c r="A328" s="3" t="n">
@@ -41210,6 +42873,11 @@
         </is>
       </c>
       <c r="M328" s="9" t="n"/>
+      <c r="N328" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="329" ht="107.8" customHeight="1">
       <c r="A329" s="3" t="n">
@@ -41265,6 +42933,11 @@
         </is>
       </c>
       <c r="M329" s="9" t="n"/>
+      <c r="N329" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="330" ht="107.8" customHeight="1">
       <c r="A330" s="3" t="n">
@@ -41310,6 +42983,11 @@
         </is>
       </c>
       <c r="M330" s="9" t="n"/>
+      <c r="N330" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="331" ht="30" customHeight="1">
       <c r="A331" s="3" t="n">
@@ -41345,6 +43023,11 @@
         </is>
       </c>
       <c r="M331" s="9" t="n"/>
+      <c r="N331" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="332" ht="107.8" customHeight="1">
       <c r="A332" s="3" t="n">
@@ -41400,6 +43083,11 @@
         </is>
       </c>
       <c r="M332" s="9" t="n"/>
+      <c r="N332" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="333" ht="107.8" customHeight="1">
       <c r="A333" s="3" t="n">
@@ -41445,6 +43133,11 @@
         </is>
       </c>
       <c r="M333" s="9" t="n"/>
+      <c r="N333" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="334" ht="30" customHeight="1">
       <c r="A334" s="3" t="n">
@@ -41485,6 +43178,11 @@
         </is>
       </c>
       <c r="M334" s="9" t="n"/>
+      <c r="N334" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="335" ht="107.8" customHeight="1">
       <c r="A335" s="3" t="n">
@@ -41540,6 +43238,11 @@
         </is>
       </c>
       <c r="M335" s="9" t="n"/>
+      <c r="N335" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="336" ht="107.8" customHeight="1">
       <c r="A336" s="3" t="n">
@@ -41585,6 +43288,11 @@
         </is>
       </c>
       <c r="M336" s="9" t="n"/>
+      <c r="N336" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="337" ht="107.8" customHeight="1">
       <c r="A337" s="3" t="n">
@@ -41630,6 +43338,11 @@
         </is>
       </c>
       <c r="M337" s="9" t="n"/>
+      <c r="N337" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="338" ht="107.8" customHeight="1">
       <c r="A338" s="3" t="n">
@@ -41675,6 +43388,11 @@
         </is>
       </c>
       <c r="M338" s="9" t="n"/>
+      <c r="N338" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="339" ht="30" customHeight="1">
       <c r="A339" s="3" t="n">
@@ -41715,6 +43433,11 @@
         </is>
       </c>
       <c r="M339" s="9" t="n"/>
+      <c r="N339" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="340" ht="107.8" customHeight="1">
       <c r="A340" s="3" t="n">
@@ -41770,6 +43493,11 @@
         </is>
       </c>
       <c r="M340" s="9" t="n"/>
+      <c r="N340" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="341" ht="107.8" customHeight="1">
       <c r="A341" s="3" t="n">
@@ -41810,6 +43538,11 @@
         </is>
       </c>
       <c r="M341" s="9" t="n"/>
+      <c r="N341" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="342" ht="30" customHeight="1">
       <c r="A342" s="3" t="n">
@@ -41850,6 +43583,11 @@
         </is>
       </c>
       <c r="M342" s="9" t="n"/>
+      <c r="N342" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="343" ht="30" customHeight="1">
       <c r="A343" s="3" t="n">
@@ -41890,6 +43628,11 @@
         </is>
       </c>
       <c r="M343" s="9" t="n"/>
+      <c r="N343" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="344" ht="107.8" customHeight="1">
       <c r="A344" s="3" t="n">
@@ -41935,6 +43678,11 @@
         </is>
       </c>
       <c r="M344" s="9" t="n"/>
+      <c r="N344" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="345" ht="30" customHeight="1">
       <c r="A345" s="3" t="n">
@@ -41975,6 +43723,11 @@
         </is>
       </c>
       <c r="M345" s="9" t="n"/>
+      <c r="N345" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="346" ht="30" customHeight="1">
       <c r="A346" s="3" t="n">
@@ -42010,6 +43763,11 @@
         </is>
       </c>
       <c r="M346" s="9" t="n"/>
+      <c r="N346" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="347" ht="107.8" customHeight="1">
       <c r="A347" s="3" t="n">
@@ -42065,6 +43823,11 @@
         </is>
       </c>
       <c r="M347" s="9" t="n"/>
+      <c r="N347" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="348" ht="107.8" customHeight="1">
       <c r="A348" s="3" t="n">
@@ -42120,6 +43883,11 @@
         </is>
       </c>
       <c r="M348" s="9" t="n"/>
+      <c r="N348" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="349" ht="107.8" customHeight="1">
       <c r="A349" s="3" t="n">
@@ -42165,6 +43933,11 @@
         </is>
       </c>
       <c r="M349" s="9" t="n"/>
+      <c r="N349" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="350" ht="30" customHeight="1">
       <c r="A350" s="3" t="n">
@@ -42200,6 +43973,11 @@
         </is>
       </c>
       <c r="M350" s="9" t="n"/>
+      <c r="N350" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="351" ht="107.8" customHeight="1">
       <c r="A351" s="3" t="n">
@@ -42255,6 +44033,11 @@
         </is>
       </c>
       <c r="M351" s="9" t="n"/>
+      <c r="N351" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="352" ht="30" customHeight="1">
       <c r="A352" s="3" t="n">
@@ -42295,6 +44078,11 @@
         </is>
       </c>
       <c r="M352" s="9" t="n"/>
+      <c r="N352" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="353" ht="107.8" customHeight="1">
       <c r="A353" s="3" t="n">
@@ -42340,6 +44128,11 @@
         </is>
       </c>
       <c r="M353" s="9" t="n"/>
+      <c r="N353" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="354" ht="107.8" customHeight="1">
       <c r="A354" s="3" t="n">
@@ -42385,6 +44178,11 @@
         </is>
       </c>
       <c r="M354" s="9" t="n"/>
+      <c r="N354" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="355" ht="107.8" customHeight="1">
       <c r="A355" s="3" t="n">
@@ -42440,6 +44238,11 @@
         </is>
       </c>
       <c r="M355" s="9" t="n"/>
+      <c r="N355" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="356" ht="107.8" customHeight="1">
       <c r="A356" s="3" t="n">
@@ -42495,6 +44298,11 @@
         </is>
       </c>
       <c r="M356" s="9" t="n"/>
+      <c r="N356" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="357" ht="107.8" customHeight="1">
       <c r="A357" s="3" t="n">
@@ -42545,6 +44353,11 @@
         </is>
       </c>
       <c r="M357" s="9" t="n"/>
+      <c r="N357" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="358" ht="30" customHeight="1">
       <c r="A358" s="3" t="n">
@@ -42580,6 +44393,11 @@
         </is>
       </c>
       <c r="M358" s="9" t="n"/>
+      <c r="N358" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="359" ht="30" customHeight="1">
       <c r="A359" s="3" t="n">
@@ -42615,6 +44433,11 @@
         </is>
       </c>
       <c r="M359" s="9" t="n"/>
+      <c r="N359" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="360" ht="30" customHeight="1">
       <c r="A360" s="3" t="n">
@@ -42650,6 +44473,11 @@
         </is>
       </c>
       <c r="M360" s="9" t="n"/>
+      <c r="N360" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="361" ht="30" customHeight="1">
       <c r="A361" s="3" t="n">
@@ -42685,6 +44513,11 @@
         </is>
       </c>
       <c r="M361" s="9" t="n"/>
+      <c r="N361" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="362" ht="107.8" customHeight="1">
       <c r="A362" s="3" t="n">
@@ -42735,6 +44568,11 @@
         </is>
       </c>
       <c r="M362" s="9" t="n"/>
+      <c r="N362" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="363" ht="107.8" customHeight="1">
       <c r="A363" s="3" t="n">
@@ -42785,6 +44623,11 @@
         </is>
       </c>
       <c r="M363" s="9" t="n"/>
+      <c r="N363" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="364" ht="30" customHeight="1">
       <c r="A364" s="3" t="n">
@@ -42820,6 +44663,11 @@
         </is>
       </c>
       <c r="M364" s="9" t="n"/>
+      <c r="N364" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="365" ht="107.8" customHeight="1">
       <c r="A365" s="3" t="n">
@@ -42875,6 +44723,11 @@
         </is>
       </c>
       <c r="M365" s="9" t="n"/>
+      <c r="N365" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="366" ht="107.8" customHeight="1">
       <c r="A366" s="3" t="n">
@@ -42925,6 +44778,11 @@
         </is>
       </c>
       <c r="M366" s="9" t="n"/>
+      <c r="N366" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="367" ht="30" customHeight="1">
       <c r="A367" s="3" t="n">
@@ -42960,6 +44818,11 @@
         </is>
       </c>
       <c r="M367" s="9" t="n"/>
+      <c r="N367" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="368" ht="30" customHeight="1">
       <c r="A368" s="3" t="n">
@@ -43000,6 +44863,11 @@
         </is>
       </c>
       <c r="M368" s="9" t="n"/>
+      <c r="N368" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="369" ht="30" customHeight="1">
       <c r="A369" s="3" t="n">
@@ -43035,6 +44903,11 @@
         </is>
       </c>
       <c r="M369" s="9" t="n"/>
+      <c r="N369" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="370" ht="107.8" customHeight="1">
       <c r="A370" s="3" t="n">
@@ -43090,6 +44963,11 @@
         </is>
       </c>
       <c r="M370" s="9" t="n"/>
+      <c r="N370" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="371" ht="30" customHeight="1">
       <c r="A371" s="3" t="n">
@@ -43125,6 +45003,11 @@
         </is>
       </c>
       <c r="M371" s="9" t="n"/>
+      <c r="N371" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="372" ht="107.8" customHeight="1">
       <c r="A372" s="3" t="n">
@@ -43180,6 +45063,11 @@
         </is>
       </c>
       <c r="M372" s="9" t="n"/>
+      <c r="N372" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="373" ht="107.8" customHeight="1">
       <c r="A373" s="3" t="n">
@@ -43225,6 +45113,11 @@
         </is>
       </c>
       <c r="M373" s="9" t="n"/>
+      <c r="N373" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="374" ht="30" customHeight="1">
       <c r="A374" s="3" t="n">
@@ -43260,6 +45153,11 @@
         </is>
       </c>
       <c r="M374" s="9" t="n"/>
+      <c r="N374" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="375" ht="30" customHeight="1">
       <c r="A375" s="3" t="n">
@@ -43300,6 +45198,11 @@
         </is>
       </c>
       <c r="M375" s="9" t="n"/>
+      <c r="N375" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="376" ht="107.8" customHeight="1">
       <c r="A376" s="3" t="n">
@@ -43350,6 +45253,11 @@
         </is>
       </c>
       <c r="M376" s="9" t="n"/>
+      <c r="N376" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="377" ht="107.8" customHeight="1">
       <c r="A377" s="3" t="n">
@@ -43405,6 +45313,11 @@
         </is>
       </c>
       <c r="M377" s="9" t="n"/>
+      <c r="N377" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="378" ht="30" customHeight="1">
       <c r="A378" s="3" t="n">
@@ -43440,6 +45353,11 @@
         </is>
       </c>
       <c r="M378" s="9" t="n"/>
+      <c r="N378" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="379" ht="30" customHeight="1">
       <c r="A379" s="3" t="n">
@@ -43480,6 +45398,11 @@
         </is>
       </c>
       <c r="M379" s="9" t="n"/>
+      <c r="N379" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="380" ht="30" customHeight="1">
       <c r="A380" s="3" t="n">
@@ -43515,6 +45438,11 @@
         </is>
       </c>
       <c r="M380" s="9" t="n"/>
+      <c r="N380" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="381" ht="107.8" customHeight="1">
       <c r="A381" s="3" t="n">
@@ -43565,6 +45493,11 @@
         </is>
       </c>
       <c r="M381" s="9" t="n"/>
+      <c r="N381" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="382" ht="30" customHeight="1">
       <c r="A382" s="3" t="n">
@@ -43605,6 +45538,11 @@
         </is>
       </c>
       <c r="M382" s="9" t="n"/>
+      <c r="N382" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="383" ht="107.8" customHeight="1">
       <c r="A383" s="3" t="n">
@@ -43650,6 +45588,11 @@
         </is>
       </c>
       <c r="M383" s="9" t="n"/>
+      <c r="N383" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="384" ht="107.8" customHeight="1">
       <c r="A384" s="3" t="n">
@@ -43695,6 +45638,11 @@
         </is>
       </c>
       <c r="M384" s="9" t="n"/>
+      <c r="N384" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="385" ht="107.8" customHeight="1">
       <c r="A385" s="3" t="n">
@@ -43750,6 +45698,11 @@
         </is>
       </c>
       <c r="M385" s="9" t="n"/>
+      <c r="N385" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="386" ht="107.8" customHeight="1">
       <c r="A386" s="3" t="n">
@@ -43795,6 +45748,11 @@
         </is>
       </c>
       <c r="M386" s="9" t="n"/>
+      <c r="N386" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="387" ht="107.8" customHeight="1">
       <c r="A387" s="3" t="n">
@@ -43850,6 +45808,11 @@
         </is>
       </c>
       <c r="M387" s="9" t="n"/>
+      <c r="N387" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="388" ht="30" customHeight="1">
       <c r="A388" s="3" t="n">
@@ -43890,6 +45853,11 @@
         </is>
       </c>
       <c r="M388" s="9" t="n"/>
+      <c r="N388" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="389" ht="30" customHeight="1">
       <c r="A389" s="3" t="n">
@@ -43930,6 +45898,11 @@
         </is>
       </c>
       <c r="M389" s="9" t="n"/>
+      <c r="N389" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="390" ht="107.8" customHeight="1">
       <c r="A390" s="3" t="n">
@@ -43980,6 +45953,11 @@
         </is>
       </c>
       <c r="M390" s="9" t="n"/>
+      <c r="N390" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="391" ht="107.8" customHeight="1">
       <c r="A391" s="3" t="n">
@@ -44025,6 +46003,11 @@
         </is>
       </c>
       <c r="M391" s="9" t="n"/>
+      <c r="N391" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="392" ht="107.8" customHeight="1">
       <c r="A392" s="3" t="n">
@@ -44075,6 +46058,11 @@
         </is>
       </c>
       <c r="M392" s="9" t="n"/>
+      <c r="N392" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="393" ht="30" customHeight="1">
       <c r="A393" s="3" t="n">
@@ -44110,6 +46098,11 @@
         </is>
       </c>
       <c r="M393" s="9" t="n"/>
+      <c r="N393" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="394" ht="30" customHeight="1">
       <c r="A394" s="3" t="n">
@@ -44150,6 +46143,11 @@
         </is>
       </c>
       <c r="M394" s="9" t="n"/>
+      <c r="N394" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="395" ht="30" customHeight="1">
       <c r="A395" s="3" t="n">
@@ -44185,6 +46183,11 @@
         </is>
       </c>
       <c r="M395" s="9" t="n"/>
+      <c r="N395" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="396" ht="107.8" customHeight="1">
       <c r="A396" s="3" t="n">
@@ -44240,6 +46243,11 @@
         </is>
       </c>
       <c r="M396" s="9" t="n"/>
+      <c r="N396" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="397" ht="107.8" customHeight="1">
       <c r="A397" s="3" t="n">
@@ -44285,6 +46293,11 @@
         </is>
       </c>
       <c r="M397" s="9" t="n"/>
+      <c r="N397" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="398" ht="30" customHeight="1">
       <c r="A398" s="3" t="n">
@@ -44325,6 +46338,11 @@
         </is>
       </c>
       <c r="M398" s="9" t="n"/>
+      <c r="N398" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="399" ht="30" customHeight="1">
       <c r="A399" s="3" t="n">
@@ -44365,6 +46383,11 @@
         </is>
       </c>
       <c r="M399" s="9" t="n"/>
+      <c r="N399" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="400" ht="107.8" customHeight="1">
       <c r="A400" s="3" t="n">
@@ -44420,6 +46443,11 @@
         </is>
       </c>
       <c r="M400" s="9" t="n"/>
+      <c r="N400" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="401" ht="107.8" customHeight="1">
       <c r="A401" s="3" t="n">
@@ -44465,6 +46493,11 @@
         </is>
       </c>
       <c r="M401" s="9" t="n"/>
+      <c r="N401" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="402" ht="30" customHeight="1">
       <c r="A402" s="3" t="n">
@@ -44500,6 +46533,11 @@
         </is>
       </c>
       <c r="M402" s="9" t="n"/>
+      <c r="N402" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="403" ht="107.8" customHeight="1">
       <c r="A403" s="3" t="n">
@@ -44555,6 +46593,11 @@
         </is>
       </c>
       <c r="M403" s="9" t="n"/>
+      <c r="N403" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="404" ht="107.8" customHeight="1">
       <c r="A404" s="3" t="n">
@@ -44600,6 +46643,11 @@
         </is>
       </c>
       <c r="M404" s="9" t="n"/>
+      <c r="N404" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="405" ht="30" customHeight="1">
       <c r="A405" s="3" t="n">
@@ -44635,6 +46683,11 @@
         </is>
       </c>
       <c r="M405" s="9" t="n"/>
+      <c r="N405" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="406" ht="107.8" customHeight="1">
       <c r="A406" s="3" t="n">
@@ -44690,6 +46743,11 @@
         </is>
       </c>
       <c r="M406" s="9" t="n"/>
+      <c r="N406" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="407" ht="30" customHeight="1">
       <c r="A407" s="3" t="n">
@@ -44730,6 +46788,11 @@
         </is>
       </c>
       <c r="M407" s="9" t="n"/>
+      <c r="N407" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="408" ht="107.8" customHeight="1">
       <c r="A408" s="3" t="n">
@@ -44785,6 +46848,11 @@
         </is>
       </c>
       <c r="M408" s="9" t="n"/>
+      <c r="N408" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="409" ht="107.8" customHeight="1">
       <c r="A409" s="3" t="n">
@@ -44835,6 +46903,11 @@
         </is>
       </c>
       <c r="M409" s="9" t="n"/>
+      <c r="N409" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="410" ht="30" customHeight="1">
       <c r="A410" s="3" t="n">
@@ -44875,6 +46948,11 @@
         </is>
       </c>
       <c r="M410" s="9" t="n"/>
+      <c r="N410" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="411" ht="107.8" customHeight="1">
       <c r="A411" s="3" t="n">
@@ -44930,6 +47008,11 @@
         </is>
       </c>
       <c r="M411" s="9" t="n"/>
+      <c r="N411" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="412" ht="30" customHeight="1">
       <c r="A412" s="3" t="n">
@@ -44970,6 +47053,11 @@
         </is>
       </c>
       <c r="M412" s="9" t="n"/>
+      <c r="N412" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="413" ht="30" customHeight="1">
       <c r="A413" s="3" t="n">
@@ -45010,6 +47098,11 @@
         </is>
       </c>
       <c r="M413" s="9" t="n"/>
+      <c r="N413" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="414" ht="107.8" customHeight="1">
       <c r="A414" s="3" t="n">
@@ -45055,6 +47148,11 @@
         </is>
       </c>
       <c r="M414" s="9" t="n"/>
+      <c r="N414" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="415" ht="107.8" customHeight="1">
       <c r="A415" s="3" t="n">
@@ -45100,6 +47198,11 @@
         </is>
       </c>
       <c r="M415" s="9" t="n"/>
+      <c r="N415" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="416" ht="107.8" customHeight="1">
       <c r="A416" s="3" t="n">
@@ -45155,6 +47258,11 @@
         </is>
       </c>
       <c r="M416" s="9" t="n"/>
+      <c r="N416" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="417" ht="30" customHeight="1">
       <c r="A417" s="3" t="n">
@@ -45195,6 +47303,11 @@
         </is>
       </c>
       <c r="M417" s="9" t="n"/>
+      <c r="N417" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="418" ht="30" customHeight="1">
       <c r="A418" s="3" t="n">
@@ -45235,6 +47348,11 @@
         </is>
       </c>
       <c r="M418" s="9" t="n"/>
+      <c r="N418" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="419" ht="107.8" customHeight="1">
       <c r="A419" s="3" t="n">
@@ -45275,6 +47393,11 @@
         </is>
       </c>
       <c r="M419" s="9" t="n"/>
+      <c r="N419" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="420" ht="30" customHeight="1">
       <c r="A420" s="3" t="n">
@@ -45315,6 +47438,11 @@
         </is>
       </c>
       <c r="M420" s="9" t="n"/>
+      <c r="N420" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="421" ht="30" customHeight="1">
       <c r="A421" s="3" t="n">
@@ -45355,6 +47483,11 @@
         </is>
       </c>
       <c r="M421" s="9" t="n"/>
+      <c r="N421" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="422" ht="30" customHeight="1">
       <c r="A422" s="3" t="n">
@@ -45390,6 +47523,11 @@
         </is>
       </c>
       <c r="M422" s="9" t="n"/>
+      <c r="N422" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="423" ht="107.8" customHeight="1">
       <c r="A423" s="3" t="n">
@@ -45445,6 +47583,11 @@
         </is>
       </c>
       <c r="M423" s="9" t="n"/>
+      <c r="N423" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="424" ht="30" customHeight="1">
       <c r="A424" s="3" t="n">
@@ -45485,6 +47628,11 @@
         </is>
       </c>
       <c r="M424" s="9" t="n"/>
+      <c r="N424" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="425" ht="107.8" customHeight="1">
       <c r="A425" s="3" t="n">
@@ -45540,6 +47688,11 @@
         </is>
       </c>
       <c r="M425" s="9" t="n"/>
+      <c r="N425" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="426" ht="107.8" customHeight="1">
       <c r="A426" s="3" t="n">
@@ -45590,6 +47743,11 @@
         </is>
       </c>
       <c r="M426" s="9" t="n"/>
+      <c r="N426" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="427" ht="30" customHeight="1">
       <c r="A427" s="3" t="n">
@@ -45625,6 +47783,11 @@
         </is>
       </c>
       <c r="M427" s="9" t="n"/>
+      <c r="N427" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="428" ht="30" customHeight="1">
       <c r="A428" s="3" t="n">
@@ -45660,6 +47823,11 @@
         </is>
       </c>
       <c r="M428" s="9" t="n"/>
+      <c r="N428" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="429" ht="30" customHeight="1">
       <c r="A429" s="3" t="n">
@@ -45695,6 +47863,11 @@
         </is>
       </c>
       <c r="M429" s="9" t="n"/>
+      <c r="N429" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="430" ht="30" customHeight="1">
       <c r="A430" s="3" t="n">
@@ -45730,6 +47903,11 @@
         </is>
       </c>
       <c r="M430" s="9" t="n"/>
+      <c r="N430" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="431" ht="30" customHeight="1">
       <c r="A431" s="3" t="n">
@@ -45765,6 +47943,11 @@
         </is>
       </c>
       <c r="M431" s="9" t="n"/>
+      <c r="N431" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="432" ht="107.8" customHeight="1">
       <c r="A432" s="3" t="n">
@@ -45815,6 +47998,11 @@
         </is>
       </c>
       <c r="M432" s="9" t="n"/>
+      <c r="N432" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="433" ht="30" customHeight="1">
       <c r="A433" s="3" t="n">
@@ -45850,6 +48038,11 @@
         </is>
       </c>
       <c r="M433" s="9" t="n"/>
+      <c r="N433" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="434" ht="30" customHeight="1">
       <c r="A434" s="3" t="n">
@@ -45885,6 +48078,11 @@
         </is>
       </c>
       <c r="M434" s="9" t="n"/>
+      <c r="N434" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="435" ht="30" customHeight="1">
       <c r="A435" s="3" t="n">
@@ -45920,6 +48118,11 @@
         </is>
       </c>
       <c r="M435" s="9" t="n"/>
+      <c r="N435" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="436" ht="30" customHeight="1">
       <c r="A436" s="3" t="n">
@@ -45955,6 +48158,11 @@
         </is>
       </c>
       <c r="M436" s="9" t="n"/>
+      <c r="N436" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="437" ht="30" customHeight="1">
       <c r="A437" s="3" t="n">
@@ -45990,6 +48198,11 @@
         </is>
       </c>
       <c r="M437" s="9" t="n"/>
+      <c r="N437" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="438" ht="30" customHeight="1">
       <c r="A438" s="3" t="n">
@@ -46025,6 +48238,11 @@
         </is>
       </c>
       <c r="M438" s="9" t="n"/>
+      <c r="N438" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="439" ht="30" customHeight="1">
       <c r="A439" s="3" t="n">
@@ -46060,6 +48278,11 @@
         </is>
       </c>
       <c r="M439" s="9" t="n"/>
+      <c r="N439" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="440" ht="107.8" customHeight="1">
       <c r="A440" s="3" t="n">
@@ -46110,6 +48333,11 @@
         </is>
       </c>
       <c r="M440" s="9" t="n"/>
+      <c r="N440" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="441" ht="30" customHeight="1">
       <c r="A441" s="3" t="n">
@@ -46145,6 +48373,11 @@
         </is>
       </c>
       <c r="M441" s="9" t="n"/>
+      <c r="N441" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="442" ht="30" customHeight="1">
       <c r="A442" s="3" t="n">
@@ -46180,6 +48413,11 @@
         </is>
       </c>
       <c r="M442" s="9" t="n"/>
+      <c r="N442" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="443" ht="107.8" customHeight="1">
       <c r="A443" s="3" t="n">
@@ -46225,6 +48463,11 @@
         </is>
       </c>
       <c r="M443" s="9" t="n"/>
+      <c r="N443" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="444" ht="107.8" customHeight="1">
       <c r="A444" s="3" t="n">
@@ -46265,6 +48508,11 @@
         </is>
       </c>
       <c r="M444" s="9" t="n"/>
+      <c r="N444" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="445" ht="30" customHeight="1">
       <c r="A445" s="3" t="n">
@@ -46300,6 +48548,11 @@
         </is>
       </c>
       <c r="M445" s="9" t="n"/>
+      <c r="N445" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="446" ht="107.8" customHeight="1">
       <c r="A446" s="3" t="n">
@@ -46350,6 +48603,11 @@
         </is>
       </c>
       <c r="M446" s="9" t="n"/>
+      <c r="N446" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="447" ht="30" customHeight="1">
       <c r="A447" s="3" t="n">
@@ -46385,6 +48643,11 @@
         </is>
       </c>
       <c r="M447" s="9" t="n"/>
+      <c r="N447" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="448" ht="30" customHeight="1">
       <c r="A448" s="3" t="n">
@@ -46420,6 +48683,11 @@
         </is>
       </c>
       <c r="M448" s="9" t="n"/>
+      <c r="N448" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="449" ht="107.8" customHeight="1">
       <c r="A449" s="3" t="n">
@@ -46465,6 +48733,11 @@
         </is>
       </c>
       <c r="M449" s="9" t="n"/>
+      <c r="N449" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="450" ht="30" customHeight="1">
       <c r="A450" s="3" t="n">
@@ -46505,6 +48778,11 @@
         </is>
       </c>
       <c r="M450" s="9" t="n"/>
+      <c r="N450" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="451" ht="107.8" customHeight="1">
       <c r="A451" s="3" t="n">
@@ -46560,6 +48838,11 @@
         </is>
       </c>
       <c r="M451" s="9" t="n"/>
+      <c r="N451" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="452" ht="107.8" customHeight="1">
       <c r="A452" s="3" t="n">
@@ -46610,6 +48893,11 @@
         </is>
       </c>
       <c r="M452" s="9" t="n"/>
+      <c r="N452" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="453" ht="30" customHeight="1">
       <c r="A453" s="3" t="n">
@@ -46645,6 +48933,11 @@
         </is>
       </c>
       <c r="M453" s="9" t="n"/>
+      <c r="N453" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="454" ht="107.8" customHeight="1">
       <c r="A454" s="3" t="n">
@@ -46695,6 +48988,11 @@
         </is>
       </c>
       <c r="M454" s="9" t="n"/>
+      <c r="N454" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="455" ht="107.8" customHeight="1">
       <c r="A455" s="3" t="n">
@@ -46750,6 +49048,11 @@
         </is>
       </c>
       <c r="M455" s="9" t="n"/>
+      <c r="N455" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="456" ht="30" customHeight="1">
       <c r="A456" s="3" t="n">
@@ -46790,6 +49093,11 @@
         </is>
       </c>
       <c r="M456" s="9" t="n"/>
+      <c r="N456" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="457" ht="107.8" customHeight="1">
       <c r="A457" s="3" t="n">
@@ -46840,6 +49148,11 @@
         </is>
       </c>
       <c r="M457" s="9" t="n"/>
+      <c r="N457" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="458" ht="107.8" customHeight="1">
       <c r="A458" s="3" t="n">
@@ -46895,6 +49208,11 @@
         </is>
       </c>
       <c r="M458" s="9" t="n"/>
+      <c r="N458" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="459" ht="107.8" customHeight="1">
       <c r="A459" s="3" t="n">
@@ -46940,6 +49258,11 @@
         </is>
       </c>
       <c r="M459" s="9" t="n"/>
+      <c r="N459" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="460" ht="107.8" customHeight="1">
       <c r="A460" s="3" t="n">
@@ -46995,6 +49318,11 @@
         </is>
       </c>
       <c r="M460" s="9" t="n"/>
+      <c r="N460" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="461" ht="107.8" customHeight="1">
       <c r="A461" s="3" t="n">
@@ -47050,6 +49378,11 @@
         </is>
       </c>
       <c r="M461" s="9" t="n"/>
+      <c r="N461" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="462" ht="107.8" customHeight="1">
       <c r="A462" s="3" t="n">
@@ -47090,6 +49423,11 @@
         </is>
       </c>
       <c r="M462" s="9" t="n"/>
+      <c r="N462" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="463" ht="30" customHeight="1">
       <c r="A463" s="3" t="n">
@@ -47125,6 +49463,11 @@
         </is>
       </c>
       <c r="M463" s="9" t="n"/>
+      <c r="N463" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="464" ht="30" customHeight="1">
       <c r="A464" s="3" t="n">
@@ -47160,6 +49503,11 @@
         </is>
       </c>
       <c r="M464" s="9" t="n"/>
+      <c r="N464" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="465" ht="107.8" customHeight="1">
       <c r="A465" s="3" t="n">
@@ -47200,6 +49548,11 @@
         </is>
       </c>
       <c r="M465" s="9" t="n"/>
+      <c r="N465" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="466" ht="30" customHeight="1">
       <c r="A466" s="3" t="n">
@@ -47240,6 +49593,11 @@
         </is>
       </c>
       <c r="M466" s="9" t="n"/>
+      <c r="N466" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="467" ht="30" customHeight="1">
       <c r="A467" s="3" t="n">
@@ -47275,6 +49633,11 @@
         </is>
       </c>
       <c r="M467" s="9" t="n"/>
+      <c r="N467" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="468" ht="30" customHeight="1">
       <c r="A468" s="3" t="n">
@@ -47315,6 +49678,11 @@
         </is>
       </c>
       <c r="M468" s="9" t="n"/>
+      <c r="N468" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="469" ht="30" customHeight="1">
       <c r="A469" s="3" t="n">
@@ -47355,6 +49723,11 @@
         </is>
       </c>
       <c r="M469" s="9" t="n"/>
+      <c r="N469" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="470" ht="107.8" customHeight="1">
       <c r="A470" s="3" t="n">
@@ -47400,6 +49773,11 @@
         </is>
       </c>
       <c r="M470" s="9" t="n"/>
+      <c r="N470" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="471" ht="107.8" customHeight="1">
       <c r="A471" s="3" t="n">
@@ -47445,6 +49823,11 @@
         </is>
       </c>
       <c r="M471" s="9" t="n"/>
+      <c r="N471" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="472" ht="30" customHeight="1">
       <c r="A472" s="3" t="n">
@@ -47485,6 +49868,11 @@
         </is>
       </c>
       <c r="M472" s="9" t="n"/>
+      <c r="N472" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="473" ht="107.8" customHeight="1">
       <c r="A473" s="3" t="n">
@@ -47540,6 +49928,11 @@
         </is>
       </c>
       <c r="M473" s="9" t="n"/>
+      <c r="N473" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="474" ht="107.8" customHeight="1">
       <c r="A474" s="3" t="n">
@@ -47585,6 +49978,11 @@
         </is>
       </c>
       <c r="M474" s="9" t="n"/>
+      <c r="N474" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="475" ht="30" customHeight="1">
       <c r="A475" s="3" t="n">
@@ -47620,6 +50018,11 @@
         </is>
       </c>
       <c r="M475" s="9" t="n"/>
+      <c r="N475" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="476" ht="30" customHeight="1">
       <c r="A476" s="3" t="n">
@@ -47660,6 +50063,11 @@
         </is>
       </c>
       <c r="M476" s="9" t="n"/>
+      <c r="N476" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="477" ht="30" customHeight="1">
       <c r="A477" s="3" t="n">
@@ -47700,6 +50108,11 @@
         </is>
       </c>
       <c r="M477" s="9" t="n"/>
+      <c r="N477" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="478" ht="107.8" customHeight="1">
       <c r="A478" s="3" t="n">
@@ -47755,6 +50168,11 @@
         </is>
       </c>
       <c r="M478" s="9" t="n"/>
+      <c r="N478" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="479" ht="107.8" customHeight="1">
       <c r="A479" s="3" t="n">
@@ -47810,6 +50228,11 @@
         </is>
       </c>
       <c r="M479" s="9" t="n"/>
+      <c r="N479" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="480" ht="107.8" customHeight="1">
       <c r="A480" s="3" t="n">
@@ -47865,6 +50288,11 @@
         </is>
       </c>
       <c r="M480" s="9" t="n"/>
+      <c r="N480" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="481" ht="30" customHeight="1">
       <c r="A481" s="3" t="n">
@@ -47900,6 +50328,11 @@
         </is>
       </c>
       <c r="M481" s="9" t="n"/>
+      <c r="N481" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="482" ht="30" customHeight="1">
       <c r="A482" s="3" t="n">
@@ -47940,6 +50373,11 @@
         </is>
       </c>
       <c r="M482" s="9" t="n"/>
+      <c r="N482" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="483" ht="107.8" customHeight="1">
       <c r="A483" s="3" t="n">
@@ -47990,6 +50428,11 @@
         </is>
       </c>
       <c r="M483" s="9" t="n"/>
+      <c r="N483" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="484" ht="107.8" customHeight="1">
       <c r="A484" s="3" t="n">
@@ -48045,6 +50488,11 @@
         </is>
       </c>
       <c r="M484" s="9" t="n"/>
+      <c r="N484" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="485" ht="30" customHeight="1">
       <c r="A485" s="3" t="n">
@@ -48085,6 +50533,11 @@
         </is>
       </c>
       <c r="M485" s="9" t="n"/>
+      <c r="N485" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="486" ht="107.8" customHeight="1">
       <c r="A486" s="3" t="n">
@@ -48140,6 +50593,11 @@
         </is>
       </c>
       <c r="M486" s="9" t="n"/>
+      <c r="N486" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="487" ht="107.8" customHeight="1">
       <c r="A487" s="3" t="n">
@@ -48195,6 +50653,11 @@
         </is>
       </c>
       <c r="M487" s="9" t="n"/>
+      <c r="N487" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="488" ht="107.8" customHeight="1">
       <c r="A488" s="3" t="n">
@@ -48240,6 +50703,11 @@
         </is>
       </c>
       <c r="M488" s="9" t="n"/>
+      <c r="N488" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="489" ht="107.8" customHeight="1">
       <c r="A489" s="3" t="n">
@@ -48295,6 +50763,11 @@
         </is>
       </c>
       <c r="M489" s="9" t="n"/>
+      <c r="N489" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="490" ht="107.8" customHeight="1">
       <c r="A490" s="3" t="n">
@@ -48340,6 +50813,11 @@
         </is>
       </c>
       <c r="M490" s="9" t="n"/>
+      <c r="N490" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="491" ht="107.8" customHeight="1">
       <c r="A491" s="3" t="n">
@@ -48385,6 +50863,11 @@
         </is>
       </c>
       <c r="M491" s="9" t="n"/>
+      <c r="N491" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="492" ht="107.8" customHeight="1">
       <c r="A492" s="3" t="n">
@@ -48430,6 +50913,11 @@
         </is>
       </c>
       <c r="M492" s="9" t="n"/>
+      <c r="N492" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="493" ht="107.8" customHeight="1">
       <c r="A493" s="3" t="n">
@@ -48485,6 +50973,11 @@
         </is>
       </c>
       <c r="M493" s="9" t="n"/>
+      <c r="N493" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="494" ht="107.8" customHeight="1">
       <c r="A494" s="3" t="n">
@@ -48535,6 +51028,11 @@
         </is>
       </c>
       <c r="M494" s="9" t="n"/>
+      <c r="N494" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="495" ht="30" customHeight="1">
       <c r="A495" s="3" t="n">
@@ -48575,6 +51073,11 @@
         </is>
       </c>
       <c r="M495" s="9" t="n"/>
+      <c r="N495" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="496" ht="107.8" customHeight="1">
       <c r="A496" s="3" t="n">
@@ -48625,6 +51128,11 @@
         </is>
       </c>
       <c r="M496" s="9" t="n"/>
+      <c r="N496" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="497" ht="107.8" customHeight="1">
       <c r="A497" s="3" t="n">
@@ -48675,6 +51183,11 @@
         </is>
       </c>
       <c r="M497" s="9" t="n"/>
+      <c r="N497" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="498" ht="30" customHeight="1">
       <c r="A498" s="3" t="n">
@@ -48710,6 +51223,11 @@
         </is>
       </c>
       <c r="M498" s="9" t="n"/>
+      <c r="N498" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="499" ht="107.8" customHeight="1">
       <c r="A499" s="3" t="n">
@@ -48755,6 +51273,11 @@
         </is>
       </c>
       <c r="M499" s="9" t="n"/>
+      <c r="N499" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="500" ht="30" customHeight="1">
       <c r="A500" s="3" t="n">
@@ -48790,6 +51313,11 @@
         </is>
       </c>
       <c r="M500" s="9" t="n"/>
+      <c r="N500" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="501" ht="30" customHeight="1">
       <c r="A501" s="3" t="n">
@@ -48825,6 +51353,11 @@
         </is>
       </c>
       <c r="M501" s="9" t="n"/>
+      <c r="N501" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="502" ht="30" customHeight="1">
       <c r="A502" s="3" t="n">
@@ -48860,6 +51393,11 @@
         </is>
       </c>
       <c r="M502" s="9" t="n"/>
+      <c r="N502" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="503" ht="107.8" customHeight="1">
       <c r="A503" s="3" t="n">
@@ -48905,6 +51443,11 @@
         </is>
       </c>
       <c r="M503" s="9" t="n"/>
+      <c r="N503" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="504" ht="107.8" customHeight="1">
       <c r="A504" s="3" t="n">
@@ -48960,6 +51503,11 @@
         </is>
       </c>
       <c r="M504" s="9" t="n"/>
+      <c r="N504" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="505" ht="107.8" customHeight="1">
       <c r="A505" s="3" t="n">
@@ -49005,6 +51553,11 @@
         </is>
       </c>
       <c r="M505" s="9" t="n"/>
+      <c r="N505" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="506" ht="107.8" customHeight="1">
       <c r="A506" s="3" t="n">
@@ -49060,6 +51613,11 @@
         </is>
       </c>
       <c r="M506" s="9" t="n"/>
+      <c r="N506" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="507" ht="107.8" customHeight="1">
       <c r="A507" s="3" t="n">
@@ -49115,6 +51673,11 @@
         </is>
       </c>
       <c r="M507" s="9" t="n"/>
+      <c r="N507" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="508" ht="30" customHeight="1">
       <c r="A508" s="3" t="n">
@@ -49155,6 +51718,11 @@
         </is>
       </c>
       <c r="M508" s="9" t="n"/>
+      <c r="N508" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="509" ht="30" customHeight="1">
       <c r="A509" s="3" t="n">
@@ -49190,6 +51758,11 @@
         </is>
       </c>
       <c r="M509" s="9" t="n"/>
+      <c r="N509" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="510" ht="107.8" customHeight="1">
       <c r="A510" s="3" t="n">
@@ -49245,6 +51818,11 @@
         </is>
       </c>
       <c r="M510" s="9" t="n"/>
+      <c r="N510" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="511" ht="107.8" customHeight="1">
       <c r="A511" s="3" t="n">
@@ -49300,6 +51878,11 @@
         </is>
       </c>
       <c r="M511" s="9" t="n"/>
+      <c r="N511" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="512" ht="107.8" customHeight="1">
       <c r="A512" s="3" t="n">
@@ -49345,6 +51928,11 @@
         </is>
       </c>
       <c r="M512" s="9" t="n"/>
+      <c r="N512" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="513" ht="107.8" customHeight="1">
       <c r="A513" s="3" t="n">
@@ -49400,6 +51988,11 @@
         </is>
       </c>
       <c r="M513" s="9" t="n"/>
+      <c r="N513" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="514" ht="107.8" customHeight="1">
       <c r="A514" s="3" t="n">
@@ -49445,6 +52038,11 @@
         </is>
       </c>
       <c r="M514" s="9" t="n"/>
+      <c r="N514" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="515" ht="30" customHeight="1">
       <c r="A515" s="3" t="n">
@@ -49485,6 +52083,11 @@
         </is>
       </c>
       <c r="M515" s="9" t="n"/>
+      <c r="N515" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="516" ht="107.8" customHeight="1">
       <c r="A516" s="3" t="n">
@@ -49540,6 +52143,11 @@
         </is>
       </c>
       <c r="M516" s="9" t="n"/>
+      <c r="N516" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="517" ht="107.8" customHeight="1">
       <c r="A517" s="3" t="n">
@@ -49595,6 +52203,11 @@
         </is>
       </c>
       <c r="M517" s="9" t="n"/>
+      <c r="N517" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="518" ht="30" customHeight="1">
       <c r="A518" s="3" t="n">
@@ -49635,6 +52248,11 @@
         </is>
       </c>
       <c r="M518" s="9" t="n"/>
+      <c r="N518" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="519" ht="107.8" customHeight="1">
       <c r="A519" s="3" t="n">
@@ -49685,6 +52303,11 @@
         </is>
       </c>
       <c r="M519" s="9" t="n"/>
+      <c r="N519" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="520" ht="107.8" customHeight="1">
       <c r="A520" s="3" t="n">
@@ -49725,6 +52348,11 @@
         </is>
       </c>
       <c r="M520" s="9" t="n"/>
+      <c r="N520" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="521" ht="107.8" customHeight="1">
       <c r="A521" s="3" t="n">
@@ -49770,6 +52398,11 @@
         </is>
       </c>
       <c r="M521" s="9" t="n"/>
+      <c r="N521" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="522" ht="107.8" customHeight="1">
       <c r="A522" s="3" t="n">
@@ -49825,6 +52458,11 @@
         </is>
       </c>
       <c r="M522" s="9" t="n"/>
+      <c r="N522" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="523" ht="30" customHeight="1">
       <c r="A523" s="3" t="n">
@@ -49865,6 +52503,11 @@
         </is>
       </c>
       <c r="M523" s="9" t="n"/>
+      <c r="N523" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="524" ht="30" customHeight="1">
       <c r="A524" s="3" t="n">
@@ -49900,6 +52543,11 @@
         </is>
       </c>
       <c r="M524" s="9" t="n"/>
+      <c r="N524" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="525" ht="30" customHeight="1">
       <c r="A525" s="3" t="n">
@@ -49940,6 +52588,11 @@
         </is>
       </c>
       <c r="M525" s="9" t="n"/>
+      <c r="N525" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="526" ht="107.8" customHeight="1">
       <c r="A526" s="3" t="n">
@@ -49990,6 +52643,11 @@
         </is>
       </c>
       <c r="M526" s="9" t="n"/>
+      <c r="N526" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="527" ht="107.8" customHeight="1">
       <c r="A527" s="3" t="n">
@@ -50045,6 +52703,11 @@
         </is>
       </c>
       <c r="M527" s="9" t="n"/>
+      <c r="N527" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="528" ht="30" customHeight="1">
       <c r="A528" s="3" t="n">
@@ -50080,6 +52743,11 @@
         </is>
       </c>
       <c r="M528" s="9" t="n"/>
+      <c r="N528" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="529" ht="30" customHeight="1">
       <c r="A529" s="3" t="n">
@@ -50120,6 +52788,11 @@
         </is>
       </c>
       <c r="M529" s="9" t="n"/>
+      <c r="N529" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="530" ht="107.8" customHeight="1">
       <c r="A530" s="3" t="n">
@@ -50175,6 +52848,11 @@
         </is>
       </c>
       <c r="M530" s="9" t="n"/>
+      <c r="N530" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="531" ht="107.8" customHeight="1">
       <c r="A531" s="3" t="n">
@@ -50225,6 +52903,11 @@
         </is>
       </c>
       <c r="M531" s="9" t="n"/>
+      <c r="N531" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="532" ht="30" customHeight="1">
       <c r="A532" s="3" t="n">
@@ -50265,6 +52948,11 @@
         </is>
       </c>
       <c r="M532" s="9" t="n"/>
+      <c r="N532" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="533" ht="107.8" customHeight="1">
       <c r="A533" s="3" t="n">
@@ -50320,6 +53008,11 @@
         </is>
       </c>
       <c r="M533" s="9" t="n"/>
+      <c r="N533" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="534" ht="107.8" customHeight="1">
       <c r="A534" s="3" t="n">
@@ -50375,6 +53068,11 @@
         </is>
       </c>
       <c r="M534" s="9" t="n"/>
+      <c r="N534" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="535" ht="30" customHeight="1">
       <c r="A535" s="3" t="n">
@@ -50415,6 +53113,11 @@
         </is>
       </c>
       <c r="M535" s="9" t="n"/>
+      <c r="N535" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="536" ht="30" customHeight="1">
       <c r="A536" s="3" t="n">
@@ -50455,6 +53158,11 @@
         </is>
       </c>
       <c r="M536" s="9" t="n"/>
+      <c r="N536" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="537" ht="107.8" customHeight="1">
       <c r="A537" s="3" t="n">
@@ -50510,6 +53218,11 @@
         </is>
       </c>
       <c r="M537" s="9" t="n"/>
+      <c r="N537" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="538" ht="107.8" customHeight="1">
       <c r="A538" s="3" t="n">
@@ -50565,6 +53278,11 @@
         </is>
       </c>
       <c r="M538" s="9" t="n"/>
+      <c r="N538" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="539" ht="30" customHeight="1">
       <c r="A539" s="3" t="n">
@@ -50605,6 +53323,11 @@
         </is>
       </c>
       <c r="M539" s="9" t="n"/>
+      <c r="N539" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="540" ht="107.8" customHeight="1">
       <c r="A540" s="3" t="n">
@@ -50660,6 +53383,11 @@
         </is>
       </c>
       <c r="M540" s="9" t="n"/>
+      <c r="N540" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="541" ht="30" customHeight="1">
       <c r="A541" s="3" t="n">
@@ -50695,6 +53423,11 @@
         </is>
       </c>
       <c r="M541" s="9" t="n"/>
+      <c r="N541" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="542" ht="107.8" customHeight="1">
       <c r="A542" s="3" t="n">
@@ -50750,6 +53483,11 @@
         </is>
       </c>
       <c r="M542" s="9" t="n"/>
+      <c r="N542" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="543" ht="30" customHeight="1">
       <c r="A543" s="3" t="n">
@@ -50790,6 +53528,11 @@
         </is>
       </c>
       <c r="M543" s="9" t="n"/>
+      <c r="N543" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="544" ht="107.8" customHeight="1">
       <c r="A544" s="3" t="n">
@@ -50845,6 +53588,11 @@
         </is>
       </c>
       <c r="M544" s="9" t="n"/>
+      <c r="N544" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="545" ht="30" customHeight="1">
       <c r="A545" s="3" t="n">
@@ -50885,6 +53633,11 @@
         </is>
       </c>
       <c r="M545" s="9" t="n"/>
+      <c r="N545" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="546" ht="107.8" customHeight="1">
       <c r="A546" s="3" t="n">
@@ -50940,6 +53693,11 @@
         </is>
       </c>
       <c r="M546" s="9" t="n"/>
+      <c r="N546" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="547" ht="107.8" customHeight="1">
       <c r="A547" s="3" t="n">
@@ -50995,6 +53753,11 @@
         </is>
       </c>
       <c r="M547" s="9" t="n"/>
+      <c r="N547" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="548" ht="107.8" customHeight="1">
       <c r="A548" s="3" t="n">
@@ -51050,6 +53813,11 @@
         </is>
       </c>
       <c r="M548" s="9" t="n"/>
+      <c r="N548" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="549" ht="107.8" customHeight="1">
       <c r="A549" s="3" t="n">
@@ -51100,6 +53868,11 @@
         </is>
       </c>
       <c r="M549" s="9" t="n"/>
+      <c r="N549" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="550" ht="107.8" customHeight="1">
       <c r="A550" s="3" t="n">
@@ -51155,6 +53928,11 @@
         </is>
       </c>
       <c r="M550" s="9" t="n"/>
+      <c r="N550" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="551" ht="107.8" customHeight="1">
       <c r="A551" s="3" t="n">
@@ -51210,6 +53988,11 @@
         </is>
       </c>
       <c r="M551" s="9" t="n"/>
+      <c r="N551" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="552" ht="107.8" customHeight="1">
       <c r="A552" s="3" t="n">
@@ -51255,6 +54038,11 @@
         </is>
       </c>
       <c r="M552" s="9" t="n"/>
+      <c r="N552" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="553" ht="107.8" customHeight="1">
       <c r="A553" s="3" t="n">
@@ -51310,6 +54098,11 @@
         </is>
       </c>
       <c r="M553" s="9" t="n"/>
+      <c r="N553" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="554" ht="30" customHeight="1">
       <c r="A554" s="3" t="n">
@@ -51350,6 +54143,11 @@
         </is>
       </c>
       <c r="M554" s="9" t="n"/>
+      <c r="N554" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="555" ht="30" customHeight="1">
       <c r="A555" s="3" t="n">
@@ -51390,6 +54188,11 @@
         </is>
       </c>
       <c r="M555" s="9" t="n"/>
+      <c r="N555" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="556" ht="107.8" customHeight="1">
       <c r="A556" s="3" t="n">
@@ -51445,6 +54248,11 @@
         </is>
       </c>
       <c r="M556" s="9" t="n"/>
+      <c r="N556" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="557" ht="107.8" customHeight="1">
       <c r="A557" s="3" t="n">
@@ -51500,6 +54308,11 @@
         </is>
       </c>
       <c r="M557" s="9" t="n"/>
+      <c r="N557" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="558" ht="30" customHeight="1">
       <c r="A558" s="3" t="n">
@@ -51540,6 +54353,11 @@
         </is>
       </c>
       <c r="M558" s="9" t="n"/>
+      <c r="N558" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="559" ht="107.8" customHeight="1">
       <c r="A559" s="3" t="n">
@@ -51595,6 +54413,11 @@
         </is>
       </c>
       <c r="M559" s="9" t="n"/>
+      <c r="N559" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="560" ht="107.8" customHeight="1">
       <c r="A560" s="3" t="n">
@@ -51640,6 +54463,11 @@
         </is>
       </c>
       <c r="M560" s="9" t="n"/>
+      <c r="N560" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="561" ht="107.8" customHeight="1">
       <c r="A561" s="3" t="n">
@@ -51685,6 +54513,11 @@
         </is>
       </c>
       <c r="M561" s="9" t="n"/>
+      <c r="N561" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="562" ht="107.8" customHeight="1">
       <c r="A562" s="3" t="n">
@@ -51740,6 +54573,11 @@
         </is>
       </c>
       <c r="M562" s="9" t="n"/>
+      <c r="N562" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="563" ht="107.8" customHeight="1">
       <c r="A563" s="3" t="n">
@@ -51785,6 +54623,11 @@
         </is>
       </c>
       <c r="M563" s="9" t="n"/>
+      <c r="N563" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="564" ht="30" customHeight="1">
       <c r="A564" s="3" t="n">
@@ -51820,6 +54663,11 @@
         </is>
       </c>
       <c r="M564" s="9" t="n"/>
+      <c r="N564" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="565" ht="30" customHeight="1">
       <c r="A565" s="3" t="n">
@@ -51855,6 +54703,11 @@
         </is>
       </c>
       <c r="M565" s="9" t="n"/>
+      <c r="N565" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="566" ht="107.8" customHeight="1">
       <c r="A566" s="3" t="n">
@@ -51910,6 +54763,11 @@
         </is>
       </c>
       <c r="M566" s="9" t="n"/>
+      <c r="N566" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="567" ht="30" customHeight="1">
       <c r="A567" s="3" t="n">
@@ -51950,6 +54808,11 @@
         </is>
       </c>
       <c r="M567" s="9" t="n"/>
+      <c r="N567" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="568" ht="107.8" customHeight="1">
       <c r="A568" s="3" t="n">
@@ -51995,6 +54858,11 @@
         </is>
       </c>
       <c r="M568" s="9" t="n"/>
+      <c r="N568" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="569" ht="107.8" customHeight="1">
       <c r="A569" s="3" t="n">
@@ -52050,6 +54918,11 @@
         </is>
       </c>
       <c r="M569" s="9" t="n"/>
+      <c r="N569" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="570" ht="107.8" customHeight="1">
       <c r="A570" s="3" t="n">
@@ -52095,6 +54968,11 @@
         </is>
       </c>
       <c r="M570" s="9" t="n"/>
+      <c r="N570" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="571" ht="107.8" customHeight="1">
       <c r="A571" s="3" t="n">
@@ -52140,6 +55018,11 @@
         </is>
       </c>
       <c r="M571" s="9" t="n"/>
+      <c r="N571" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="572" ht="30" customHeight="1">
       <c r="A572" s="3" t="n">
@@ -52180,6 +55063,11 @@
         </is>
       </c>
       <c r="M572" s="9" t="n"/>
+      <c r="N572" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="573" ht="107.8" customHeight="1">
       <c r="A573" s="3" t="n">
@@ -52235,6 +55123,11 @@
         </is>
       </c>
       <c r="M573" s="9" t="n"/>
+      <c r="N573" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="574" ht="30" customHeight="1">
       <c r="A574" s="3" t="n">
@@ -52275,6 +55168,11 @@
         </is>
       </c>
       <c r="M574" s="9" t="n"/>
+      <c r="N574" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="575" ht="107.8" customHeight="1">
       <c r="A575" s="3" t="n">
@@ -52330,6 +55228,11 @@
         </is>
       </c>
       <c r="M575" s="9" t="n"/>
+      <c r="N575" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="576" ht="107.8" customHeight="1">
       <c r="A576" s="3" t="n">
@@ -52385,6 +55288,11 @@
         </is>
       </c>
       <c r="M576" s="9" t="n"/>
+      <c r="N576" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="577" ht="107.8" customHeight="1">
       <c r="A577" s="3" t="n">
@@ -52430,6 +55338,11 @@
         </is>
       </c>
       <c r="M577" s="9" t="n"/>
+      <c r="N577" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="578" ht="107.8" customHeight="1">
       <c r="A578" s="3" t="n">
@@ -52485,6 +55398,11 @@
         </is>
       </c>
       <c r="M578" s="9" t="n"/>
+      <c r="N578" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="579" ht="107.8" customHeight="1">
       <c r="A579" s="3" t="n">
@@ -52540,6 +55458,11 @@
         </is>
       </c>
       <c r="M579" s="9" t="n"/>
+      <c r="N579" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="580" ht="107.8" customHeight="1">
       <c r="A580" s="3" t="n">
@@ -52595,6 +55518,11 @@
         </is>
       </c>
       <c r="M580" s="9" t="n"/>
+      <c r="N580" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="581" ht="107.8" customHeight="1">
       <c r="A581" s="3" t="n">
@@ -52650,6 +55578,11 @@
         </is>
       </c>
       <c r="M581" s="9" t="n"/>
+      <c r="N581" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="582" ht="107.8" customHeight="1">
       <c r="A582" s="3" t="n">
@@ -52705,6 +55638,11 @@
         </is>
       </c>
       <c r="M582" s="9" t="n"/>
+      <c r="N582" s="16" t="inlineStr">
+        <is>
+          <t>oude zoekronde</t>
+        </is>
+      </c>
     </row>
     <row r="583" ht="107.8" customHeight="1">
       <c r="A583" s="3" t="n">
@@ -52750,6 +55688,11 @@
         </is>
       </c>
       <c r="M583" s="9" t="n"/>
+      <c r="N583" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="584" ht="107.8" customHeight="1">
       <c r="A584" s="3" t="n">
@@ -52805,6 +55748,11 @@
         </is>
       </c>
       <c r="M584" s="9" t="n"/>
+      <c r="N584" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="585" ht="30" customHeight="1">
       <c r="A585" s="3" t="n">
@@ -52845,6 +55793,11 @@
         </is>
       </c>
       <c r="M585" s="9" t="n"/>
+      <c r="N585" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="586" ht="107.8" customHeight="1">
       <c r="A586" s="3" t="n">
@@ -52900,6 +55853,11 @@
         </is>
       </c>
       <c r="M586" s="9" t="n"/>
+      <c r="N586" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="587" ht="107.8" customHeight="1">
       <c r="A587" s="3" t="n">
@@ -52955,6 +55913,11 @@
         </is>
       </c>
       <c r="M587" s="9" t="n"/>
+      <c r="N587" s="14" t="inlineStr">
+        <is>
+          <t>hoofdafbeelding</t>
+        </is>
+      </c>
     </row>
     <row r="588" ht="30" customHeight="1">
       <c r="A588" s="3" t="n">
@@ -52995,6 +55958,11 @@
         </is>
       </c>
       <c r="M588" s="9" t="n"/>
+      <c r="N588" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="589" ht="30" customHeight="1">
       <c r="A589" s="3" t="n">
@@ -53035,6 +56003,11 @@
         </is>
       </c>
       <c r="M589" s="9" t="n"/>
+      <c r="N589" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="590" ht="30" customHeight="1">
       <c r="A590" s="3" t="n">
@@ -53075,6 +56048,11 @@
         </is>
       </c>
       <c r="M590" s="9" t="n"/>
+      <c r="N590" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
     <row r="591" ht="107.8" customHeight="1">
       <c r="A591" s="3" t="n">
@@ -53130,9 +56108,14 @@
         </is>
       </c>
       <c r="M591" s="9" t="n"/>
+      <c r="N591" s="15" t="inlineStr">
+        <is>
+          <t>geen foto</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M591"/>
+  <autoFilter ref="A1:N591"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId2"/>
